--- a/public/prices/price-current.xlsx
+++ b/public/prices/price-current.xlsx
@@ -87,7 +87,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -349,13 +349,22 @@
       </top>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -453,6 +462,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -830,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1114"/>
+  <dimension ref="B1:F1114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="11.25"/>
   <cols>
     <col width="2.6640625" customWidth="1" min="1" max="1"/>
@@ -896,15 +908,15 @@
           <t>CAREPROST</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n"/>
+      <c r="C6" s="43" t="n"/>
       <c r="D6" s="24" t="n"/>
-      <c r="E6" s="25" t="n"/>
-      <c r="F6" s="26" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="44" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Ср-во д/быстрого роста ресниц 3 мл. 0604</t>
+          <t>Средство для быстрого роста ресниц 3мл 0604</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -926,15 +938,15 @@
           <t>CONCEPT</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n"/>
+      <c r="C8" s="43" t="n"/>
       <c r="D8" s="24" t="n"/>
-      <c r="E8" s="25" t="n"/>
-      <c r="F8" s="26" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Цера-бальзам д/губ ультраувлажняющий 13мл 52803</t>
+          <t>Бальзам для губ ультраувлажняющий 13мл 52803</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -951,7 +963,7 @@
     <row r="10" ht="22.5" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Бальзам оттеночный  Эффект пепл.блонд 300мл.ANTI-yellow 92015/39127</t>
+          <t>Бальзам оттеночный эффект пепельный блонд 300мл 92015/39127</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
@@ -970,7 +982,7 @@
     <row r="11">
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Дозатор д/флакона 1000мл 23997</t>
+          <t>Дозатор для флакона 1000мл 23997</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
@@ -989,7 +1001,7 @@
     <row r="12" ht="22.5" customHeight="1">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ST Soft Care Кондиционер д/бережного ухода за повр.волосами 300мл 91766</t>
+          <t>Кондиционер для бережного ухода за поврежденными волосами 300мл 91766</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -1008,7 +1020,7 @@
     <row r="13">
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>BEAUTY curls Кондиционер д/вьющихся волос 300мл 31091/94873</t>
+          <t>Кондиционер для вьющихся волос 300мл 31091/94873</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -1027,7 +1039,7 @@
     <row r="14" ht="22.5" customHeight="1">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Кондиционер с пептидным комплексом  для нейт.желтизны ПЛАТИНА ,Next Level Blond,1000мл 99625</t>
+          <t>Кондиционер с пептидным комплексом для нейтрализации желтизны, платина 1000мл 99625</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
@@ -1046,7 +1058,7 @@
     <row r="15">
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>BEAUTY cursl Крем д/укладки вьющихся волос 100мл 90318/38281</t>
+          <t>Крем для укладки вьющихся волос 100мл 90318/38281</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -1065,7 +1077,7 @@
     <row r="16">
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>PT Крем-краска д/бровей и ресн.графит 30/20мл 90080/20309</t>
+          <t>Крем-краска для бровей и ресниц графит 30/20мл 90080/20309</t>
         </is>
       </c>
       <c r="C16" s="32" t="n">
@@ -1084,7 +1096,7 @@
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>PT Крем-краска д/бровей и ресн.черный 30/20мл 90103/20330</t>
+          <t>Крем-краска для бровей и ресниц черный 30/20мл 90103/20330</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -1103,7 +1115,7 @@
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ST Color Маска д/окрашенных волос 500мл 90714</t>
+          <t>Color Маска для окрашенных волос 500мл 90714</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -1122,7 +1134,7 @@
     <row r="19" ht="22.5" customHeight="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>BIO CURL Набор д/хол.перман.завивки, прикорн.объем 100/100 91292</t>
+          <t>BIO CURL Набор для холодной перманентной завивки, прикорневой объём 100/100 91292</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -1198,7 +1210,7 @@
     <row r="23">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Порошок для Деликат. осветления волос,SOFT BLUE.500гр 91322</t>
+          <t>Порошок для деликатного осветления волос SOFT BLUE 500гр 91322</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
@@ -1217,7 +1229,7 @@
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Спрей двухфазный 10 в 1 д/тонких и норм.волос 240мл,Basik 90608</t>
+          <t>Спрей двухфазный 10 в 1 для тонких и нормальных волос 240мл 90608</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -1236,7 +1248,7 @@
     <row r="25">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>ST Hydro Спрей увлажняющий с термозащитой 240мл 2021 90615</t>
+          <t>Спрей увлажняющий с термозащитой 240мл 2021 90615</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -1274,7 +1286,7 @@
     <row r="27" ht="22.5" customHeight="1">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>ST Soft Care Шампунь бессульфатный д/деликатного очищения 1000мл не заказывать! 91247</t>
+          <t>Шампунь бессульфатный для деликатного очищения 1000мл 91247</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -1293,7 +1305,7 @@
     <row r="28" ht="22.5" customHeight="1">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>ST Soft Care Шампунь бессульфатный д/деликатного очищения 300мл 91254</t>
+          <t>Шампунь бессульфатный для деликатного очищения 300мл 91254</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -1312,7 +1324,7 @@
     <row r="29" ht="22.5" customHeight="1">
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Шампунь серебристый  д/св.оттенков 300мл,ANTI-yellow 91988/12359</t>
+          <t>Шампунь оттеночный серебристый ANTI-yellow 300мл 91988/12359</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -1334,15 +1346,15 @@
           <t>DIKSON</t>
         </is>
       </c>
-      <c r="C30" s="16" t="n"/>
+      <c r="C30" s="43" t="n"/>
       <c r="D30" s="24" t="n"/>
-      <c r="E30" s="25" t="n"/>
-      <c r="F30" s="26" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="44" t="n"/>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>RISTRUTTURANTE Комплекс реструктурирующий в ампулах 12х12 мл. 1127</t>
+          <t>Комплекс реструктурирующий в ампулах RISTRUTTURANTE 12х12мл 1127</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -1361,7 +1373,7 @@
     <row r="32" ht="22.5" customHeight="1">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Ср-во д/волос и кожи головы, защитный и тонизирующий эффект пчелиного молочка 10х10 мл. 0100 PAPPA REALE 1135</t>
+          <t>Средство для волос и кожи головы в ампулах, защитный и тонизирующий эффект пчелиного молочка 10х10мл 0100 PAPPA REALE 1135</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -1383,10 +1395,10 @@
           <t>ISKARTES PROFESSIONAL</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n"/>
+      <c r="C33" s="43" t="n"/>
       <c r="D33" s="24" t="n"/>
-      <c r="E33" s="25" t="n"/>
-      <c r="F33" s="26" t="n"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="44" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="31" t="inlineStr">
@@ -1410,7 +1422,7 @@
     <row r="35">
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>Дозаторы универ 644</t>
+          <t>Дозатор универсальный 644</t>
         </is>
       </c>
       <c r="C35" s="32" t="n">
@@ -1448,7 +1460,7 @@
     <row r="37" ht="22.5" customHeight="1">
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>Маска для восстановления волос с кератином Mask with keratin 500мл 644073</t>
+          <t>Маска для восстановления волос с кератином 500мл 644073</t>
         </is>
       </c>
       <c r="C37" s="32" t="n">
@@ -1467,7 +1479,7 @@
     <row r="38">
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>Маска для окрашенных волос ,500мл 644103</t>
+          <t>Маска для окрашенных волос 500мл 644103</t>
         </is>
       </c>
       <c r="C38" s="32" t="n">
@@ -1489,15 +1501,15 @@
           <t>KAPOUS</t>
         </is>
       </c>
-      <c r="C39" s="16" t="n"/>
+      <c r="C39" s="43" t="n"/>
       <c r="D39" s="24" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="26" t="n"/>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="44" t="n"/>
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>2-х фазная для волос с антижелтым эффектом «Blond Bar» 200 мл 2559</t>
+          <t>Сыворотка 2-х фазная для волос с антижелтым эффектом «Blond Bar» 200мл 2559</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -1516,7 +1528,7 @@
     <row r="41" ht="22.5" customHeight="1">
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>2-х фазная увлажняющая сыворотка с маслами авокадо 200мл 1673</t>
+          <t>Сыворотка 2-х фазная увлажняющая с маслами авокадо 200мл 1673</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
@@ -1535,7 +1547,7 @@
     <row r="42">
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>бальзам д/всех типов волос "Банан и Дыня" 1000 мл 1194/55154</t>
+          <t>Бальзам для всех типов волос "Банан и Дыня" 1000мл 1194/55154</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -1554,7 +1566,7 @@
     <row r="43">
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>бальзам д/всех типов" Молочко миндального ореха" 1000 мл 1198</t>
+          <t>Бальзам для всех типов "Молочко миндального ореха" 1000мл 1198</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -1573,7 +1585,7 @@
     <row r="44">
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Бальзам с маслом ореха макадамии 300 мл 2790</t>
+          <t>Бальзам с маслом ореха макадамии 300мл 2790</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -1592,7 +1604,7 @@
     <row r="45">
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Бальзам с маслом ореха макадамии 750 мл 2791</t>
+          <t>Бальзам с маслом ореха макадамии 750мл 2791</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -1611,7 +1623,7 @@
     <row r="46" ht="22.5" customHeight="1">
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Бальзам увлажняющий с с маслами Авокадо и Оливы 350 мл STUDIO 2638</t>
+          <t>Бальзам увлажняющий с маслами Авокадо и Оливы 350мл 2638</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -1630,7 +1642,7 @@
     <row r="47">
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>бальзам-маска  для всех типов волос волос 1050 мл 3026/18</t>
+          <t>Бальзам-маска для всех типов волос 1050мл 3026/18</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -1649,7 +1661,7 @@
     <row r="48" ht="22.5" customHeight="1">
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Бальзам-Сатин с протеинами шелка и маслом хлопка серии "Luxe Care" линии Studio Professional, 1000мл 2596</t>
+          <t>Бальзам-Сатин с протеинами шелка и маслом хлопка серии "Luxe Care" 1000мл 2596</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
@@ -1668,7 +1680,7 @@
     <row r="49" ht="22.5" customHeight="1">
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Бальзам-Шелк с протеинами шелка серии "Luxe Care" линии Studio Professional, 1000 мл 2598</t>
+          <t>Бальзам-Шелк с протеинами шелка серии "Luxe Care" 1000мл 2598</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -1687,7 +1699,7 @@
     <row r="50">
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Гель после бритья с охл. эффектом, 250 мл 2921</t>
+          <t>Гель после бритья с охлаждающим эффектом 250мл 2921</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -1704,7 +1716,7 @@
     <row r="51">
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Гель увл  муж с экстрактом оливы, 250 мл 1151</t>
+          <t>Гель увлажняющий для душа, мужской с экстрактом оливы 250мл 1151</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -1721,7 +1733,7 @@
     <row r="52">
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Гель увл  муж с экстрактом оливы, 300 мл 3225</t>
+          <t>Гель увлажняющий для душа, мужской с экстрактом оливы 300мл 3225</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -1738,7 +1750,7 @@
     <row r="53">
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>кератин бальзам "Magic Keratin" 1000 мл. 1256</t>
+          <t>Бальзам с кератином "Magic Keratin" 1000мл 1256</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -1757,7 +1769,7 @@
     <row r="54">
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Лак Kapous STUDIO  сильной фиксации, 500 мл 582</t>
+          <t>Лак STUDIO сильной фиксации 500мл 582</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -1776,7 +1788,7 @@
     <row r="55">
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Лак Kapous STUDIO НФ, 500 мл 583</t>
+          <t>Лак STUDIO нормальной фиксации 500мл 583</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -1795,7 +1807,7 @@
     <row r="56" ht="22.5" customHeight="1">
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Маска для волос с глиоксиловой кислотой из серии Glyoxy Sleek Hair,1000 мл 1478</t>
+          <t>Маска для волос с глиоксиловой кислотой из серии 1000мл 1478</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -1814,7 +1826,7 @@
     <row r="57">
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Маска для волос с маслом ореха макадамии,750 мл 2775</t>
+          <t>Маска для волос с маслом ореха макадамии 750мл 2775</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -1833,7 +1845,7 @@
     <row r="58" ht="22.5" customHeight="1">
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Маска пит. для волос Kapous Studio Professional «Oliva &amp; Avocado»,750 мл 2773</t>
+          <t>Маска питательная для волос «Oliva &amp; Avocado» 750мл 2773</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -1852,7 +1864,7 @@
     <row r="59">
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Маска с антижелтым  эффектом  "Antiyellow" 250 мл. 2715</t>
+          <t>Маска с антижелтым эффектом "Antiyellow" 250мл 2715</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -1871,7 +1883,7 @@
     <row r="60" ht="22.5" customHeight="1">
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>маска с бамбуком и пшеницей, питательная восстанавливающая "Professional" 750 мл 3189</t>
+          <t>Маска с экстрктом бамбука и пшеници, питательная восстанавливающая 750мл 3189</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -1890,7 +1902,7 @@
     <row r="61" ht="22.5" customHeight="1">
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Окислительная эмульсия «Hyaluronic Cremoxon» с Гиалуроновой кислотой 6%,1050 мл 3022/6%</t>
+          <t>Окислительная эмульсия «Hyaluronic Cremoxon» с Гиалуроновой кислотой 6% 1050мл 3022/6%</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -1909,7 +1921,7 @@
     <row r="62">
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>оксид ВВ с экстрактом жемчуга 12% 200мл 2473,200МЛ</t>
+          <t>Окислительная эмульсия ВВ с экстрактом жемчуга 12% 200мл 2473,200МЛ</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
@@ -1928,7 +1940,7 @@
     <row r="63">
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Пена мужская д/бритья GENTLEMEN 3 effect 300 мл. 923</t>
+          <t>Пена мужская для бритья GENTLEMEN 3 effect 300мл 923</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -1945,7 +1957,7 @@
     <row r="64">
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Сыв-ка с пшеничными протеинами 500 мл. 1219</t>
+          <t>Сыворотка с пшеничными протеинами 500мл 1219</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
@@ -1964,7 +1976,7 @@
     <row r="65">
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Флюид д/секущ. кончиков с маслами Авокадо и Оливы,80мл 1672</t>
+          <t>Флюид для секущихся кончиков с маслами Авокадо и Оливы 80мл 1672</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -1983,7 +1995,7 @@
     <row r="66">
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Шампунь анти-желтый STUDIO.250мл 2736</t>
+          <t>Шампунь анти-желтый 250мл 2736</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -2002,7 +2014,7 @@
     <row r="67">
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Шампунь д/выпрямления "GlyoxySleek Hair"  1000мл 1479</t>
+          <t>Шампунь для выпрямления волос 1000мл 1479</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -2021,7 +2033,7 @@
     <row r="68">
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Шампунь д/жирных волос 300 мл. 3134</t>
+          <t>Шампунь для жирных волос 300мл 3134</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -2040,7 +2052,7 @@
     <row r="69">
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Шампунь мицеллярный для волос 300 мл 2917</t>
+          <t>Шампунь мицеллярный для волос 300мл 2917</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -2078,7 +2090,7 @@
     <row r="71">
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Шампунь мужской тонизирующий 3 в 1 "Gentelmen" 250 мл 868</t>
+          <t>Шампунь мужской тонизирующий 3 в 1 "Gentelmen" 250мл 868</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
@@ -2097,7 +2109,7 @@
     <row r="72" ht="22.5" customHeight="1">
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Шампунь оттеночный блонд,Стальной, 200 мл  “Blond Bar”, 200мл 2696</t>
+          <t>Шампунь оттеночный, стальной 200мл 2696</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
@@ -2116,7 +2128,7 @@
     <row r="73">
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Шампунь с маслом ореха макадамии 750 мл 2789</t>
+          <t>Шампунь с маслом ореха макадамии 750мл 2789</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
@@ -2135,7 +2147,7 @@
     <row r="74">
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Шампунь сухой для волос «Fresh&amp;Up», 150 мл 2553</t>
+          <t>Шампунь сухой для волос 150мл 2553</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -2157,10 +2169,10 @@
           <t>L'OREAL</t>
         </is>
       </c>
-      <c r="C75" s="16" t="n"/>
+      <c r="C75" s="43" t="n"/>
       <c r="D75" s="24" t="n"/>
-      <c r="E75" s="25" t="n"/>
-      <c r="F75" s="26" t="n"/>
+      <c r="E75" s="24" t="n"/>
+      <c r="F75" s="44" t="n"/>
     </row>
     <row r="76">
       <c r="B76" s="7" t="inlineStr">
@@ -2222,7 +2234,7 @@
     <row r="79">
       <c r="B79" s="31" t="inlineStr">
         <is>
-          <t>INOA Aktyvator 3% (10 vol.) 1000 ml. 17762</t>
+          <t>INOA Aktyvator 3% (10 vol.) 1000мл 17762</t>
         </is>
       </c>
       <c r="C79" s="36" t="n">
@@ -2320,15 +2332,15 @@
           <t>LEBEL</t>
         </is>
       </c>
-      <c r="C84" s="16" t="n"/>
+      <c r="C84" s="43" t="n"/>
       <c r="D84" s="24" t="n"/>
-      <c r="E84" s="25" t="n"/>
-      <c r="F84" s="26" t="n"/>
+      <c r="E84" s="24" t="n"/>
+      <c r="F84" s="44" t="n"/>
     </row>
     <row r="85">
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>№1 Сыв-ка д/волос  PROEDIT CARE WORKS  CMC 150 мл. 2849</t>
+          <t>№1 Сыворотка для волос PROEDIT CARE WORKS CMC 150мл 2849</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
@@ -2347,7 +2359,7 @@
     <row r="86">
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>№1 Сыв-ка д/волос  PROEDIT CARE WORKS  CMC 500 мл. 3372</t>
+          <t>№1 Сыворотка для волос PROEDIT CARE WORKS CMC 500мл 3372</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
@@ -2366,7 +2378,7 @@
     <row r="87">
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>№2 Сыв-ка д/волос  PROEDIT CARE WORKS NMF 150 мл. 2863</t>
+          <t>№2 Сыворотка для волос PROEDIT CARE WORKS NMF 150мл 2863</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
@@ -2385,7 +2397,7 @@
     <row r="88">
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>№2 Сыв-ка д/волос  PROEDIT CARE WORKS NMF 500 мл. 3389</t>
+          <t>№2 Сыворотка для волос PROEDIT CARE WORKS NMF 500мл 3389</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
@@ -2404,7 +2416,7 @@
     <row r="89">
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>№3 Сыв-ка д/волос  PROEDIT CARE WORKS PPT 150 мл. 2856</t>
+          <t>№3 Сыворотка для волос PROEDIT CARE WORKS PPT 150мл 2856</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
@@ -2423,7 +2435,7 @@
     <row r="90">
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>№3 Сыв-ка д/волос  PROEDIT CARE WORKS PPT 500мл 3396</t>
+          <t>№3 Сыворотка для волос PROEDIT CARE WORKS PPT 500мл 3396</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
@@ -2442,7 +2454,7 @@
     <row r="91" ht="22.5" customHeight="1">
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>№4 Сыв-ка д/волос  PROEDIT CARE WORKS ELEMENT FIX 150 мл. 2870</t>
+          <t>№4 Сыворотка для волос PROEDIT CARE WORKS ELEMENT FIX 150мл 2870</t>
         </is>
       </c>
       <c r="C91" s="10" t="n">
@@ -2461,7 +2473,7 @@
     <row r="92" ht="22.5" customHeight="1">
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>№4 Сыв-ка д/волос  PROEDIT CARE WORKS ELEMENT FIX 500 мл. 3402</t>
+          <t>№4 Сыворотка для волос PROEDIT CARE WORKS ELEMENT FIX 500мл 3402</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
@@ -2480,7 +2492,7 @@
     <row r="93">
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>АромаКрем "Silky Repair" для укрепления волос, 1000 мл 4300</t>
+          <t>АромаКрем "Silky Repair" для укрепления волос 1000мл 4300</t>
         </is>
       </c>
       <c r="C93" s="10" t="n">
@@ -2499,7 +2511,7 @@
     <row r="94">
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>АромаКрем "Silky Repair" для укрепления волос, 200 мл. 4119</t>
+          <t>АромаКрем "Silky Repair" для укрепления волос 200мл 4119</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
@@ -2518,7 +2530,7 @@
     <row r="95" ht="22.5" customHeight="1">
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>АромаМаска  д/сух., поврежд. волос IAU SERUM MASK, 170 гр. (белая) 5482</t>
+          <t>АромаМаска для сухих и поврежденных волос IAU SERUM MASK 170гр (белая) 5482</t>
         </is>
       </c>
       <c r="C95" s="10" t="n">
@@ -2537,7 +2549,7 @@
     <row r="96" ht="22.5" customHeight="1">
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>АромаМаска "Deep" д/восст. непослуш волос, 170 гр. (сиреневая) 4492</t>
+          <t>АромаМаска "Deep" для восстановления непослуных волос 170гр (сиреневая) 4492</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
@@ -2556,7 +2568,7 @@
     <row r="97" ht="22.5" customHeight="1">
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>АромаМаска "Mask" для интенсивного восстановления волос, 170 гр. (красная) 4133</t>
+          <t>АромаМаска "Mask" для интенсивного восстановления волос 170гр (красная) 4133</t>
         </is>
       </c>
       <c r="C97" s="10" t="n">
@@ -2594,7 +2606,7 @@
     <row r="99">
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>АромаШампунь "Cleаrment" очищ. д/всех типов волос, 200 мл. 4096</t>
+          <t>АромаШампунь "Cleаrment" очищающий для всех типов волос 200мл 4096</t>
         </is>
       </c>
       <c r="C99" s="10" t="n">
@@ -2613,7 +2625,7 @@
     <row r="100">
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Гель фиксирующий IAU CELL CARE (4)1000ml 5277</t>
+          <t>Гель фиксирующий IAU CELL CARE (4)1000мл 5277</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
@@ -2632,7 +2644,7 @@
     <row r="101">
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Гель фиксирующий IAU CELL CARE (4)500ml 5260</t>
+          <t>Гель фиксирующий IAU CELL CARE (4)500мл 5260</t>
         </is>
       </c>
       <c r="C101" s="10" t="n">
@@ -2727,7 +2739,7 @@
     <row r="106">
       <c r="B106" s="31" t="inlineStr">
         <is>
-          <t>Корпус металл. для мягкой упаковки 1000мл 2425лр</t>
+          <t>Корпус металлический для мягкой упаковки 1000мл 2425лр</t>
         </is>
       </c>
       <c r="C106" s="32" t="n">
@@ -2746,7 +2758,7 @@
     <row r="107">
       <c r="B107" s="31" t="inlineStr">
         <is>
-          <t>Корпус пласт. для мягкой упаковки (уход) 1000мл Lebel ONE 1725лр</t>
+          <t>Корпус пластиковый для мягкой упаковки (уход) 1000мл Lebel ONE 1725лр</t>
         </is>
       </c>
       <c r="C107" s="32" t="n">
@@ -2765,7 +2777,7 @@
     <row r="108" ht="22.5" customHeight="1">
       <c r="B108" s="31" t="inlineStr">
         <is>
-          <t>Корпус пласт. для мягкой упаковки (шампунь) 1000мл Lebel ONE 1718лр</t>
+          <t>Корпус пластиковый для мягкой упаковки (шампунь) 1000мл Lebel ONE 1718лр</t>
         </is>
       </c>
       <c r="C108" s="32" t="n">
@@ -2784,7 +2796,7 @@
     <row r="109">
       <c r="B109" s="31" t="inlineStr">
         <is>
-          <t>Корпус пласт. для мягкой упаковки 1000мл Lebel ONE 1732лр</t>
+          <t>Корпус пластиковый для мягкой упаковки 1000мл Lebel ONE 1732лр</t>
         </is>
       </c>
       <c r="C109" s="32" t="n">
@@ -2803,7 +2815,7 @@
     <row r="110">
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G A-6 0092</t>
+          <t>Материя G 120мл A-6 0092</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
@@ -2822,7 +2834,7 @@
     <row r="111">
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G A-8 0108</t>
+          <t>Материя G 120мл A-8 0108</t>
         </is>
       </c>
       <c r="C111" s="10" t="n">
@@ -2841,7 +2853,7 @@
     <row r="112">
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G B-5 9559</t>
+          <t>Материя G 120мл B-5 9559</t>
         </is>
       </c>
       <c r="C112" s="10" t="n">
@@ -2860,7 +2872,7 @@
     <row r="113">
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G Be-8 9818/Be-8</t>
+          <t>Материя G 120мл Be-8 9818/Be-8</t>
         </is>
       </c>
       <c r="C113" s="10" t="n">
@@ -2879,7 +2891,7 @@
     <row r="114">
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G CB-3 9474</t>
+          <t>Материя G 120мл CB-3 9474</t>
         </is>
       </c>
       <c r="C114" s="10" t="n">
@@ -2898,7 +2910,7 @@
     <row r="115">
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G CB-6 120гр 9504</t>
+          <t>Материя G 120мл CB-6 120гр 9504</t>
         </is>
       </c>
       <c r="C115" s="10" t="n">
@@ -2917,7 +2929,7 @@
     <row r="116">
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G G-8 0047</t>
+          <t>Материя G 120мл G-8 0047</t>
         </is>
       </c>
       <c r="C116" s="10" t="n">
@@ -2936,7 +2948,7 @@
     <row r="117">
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G M-10 120гр 0085</t>
+          <t>Материя G 120мл M-10 120гр 0085</t>
         </is>
       </c>
       <c r="C117" s="10" t="n">
@@ -2955,7 +2967,7 @@
     <row r="118">
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G M-6 120 г 0061лп</t>
+          <t>Материя G 120мл M-6 120г 0061лп</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
@@ -2974,7 +2986,7 @@
     <row r="119">
       <c r="B119" s="31" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G M-8 120 г 0078лп</t>
+          <t>Материя G 120мл M-8 120г 0078лп</t>
         </is>
       </c>
       <c r="C119" s="36" t="n">
@@ -2993,7 +3005,7 @@
     <row r="120">
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G OBe-8 120 г 9764лп</t>
+          <t>Материя G 120мл OBe-8 120г 9764лп</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
@@ -3012,7 +3024,7 @@
     <row r="121">
       <c r="B121" s="31" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G P-6 0184</t>
+          <t>Материя G 120мл P-6 0184</t>
         </is>
       </c>
       <c r="C121" s="36" t="n">
@@ -3031,7 +3043,7 @@
     <row r="122">
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G PBe-8 9719</t>
+          <t>Материя G 120мл PBe-8 9719</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
@@ -3050,7 +3062,7 @@
     <row r="123">
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G V-10 0177</t>
+          <t>Материя G 120мл V-10 0177</t>
         </is>
       </c>
       <c r="C123" s="10" t="n">
@@ -3069,7 +3081,7 @@
     <row r="124">
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос NEW G WB-7 9658</t>
+          <t>Материя G 120мл WB-7 9658</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
@@ -3088,7 +3100,7 @@
     <row r="125">
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ A-6 8538</t>
+          <t>Материя 80мл A-6 8538</t>
         </is>
       </c>
       <c r="C125" s="10" t="n">
@@ -3107,7 +3119,7 @@
     <row r="126">
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ BB MIX 8521</t>
+          <t>Материя 80мл BB MIX 8521</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
@@ -3126,7 +3138,7 @@
     <row r="127">
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ CA-6 8576</t>
+          <t>Материя 80мл CA-6 8576</t>
         </is>
       </c>
       <c r="C127" s="10" t="n">
@@ -3145,7 +3157,7 @@
     <row r="128">
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ CA-8 8583</t>
+          <t>Материя 80мл CA-8 8583</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
@@ -3164,7 +3176,7 @@
     <row r="129">
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ CB-14 7920/0-CB-14</t>
+          <t>Материя 80мл CB-14 7920/0-CB-14</t>
         </is>
       </c>
       <c r="C129" s="10" t="n">
@@ -3183,7 +3195,7 @@
     <row r="130">
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ CB-5 7852</t>
+          <t>Материя 80мл CB-5 7852</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
@@ -3202,7 +3214,7 @@
     <row r="131">
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ CB-6 7869/0-CB-6</t>
+          <t>Материя 80мл CB-6 7869/0-CB-6</t>
         </is>
       </c>
       <c r="C131" s="10" t="n">
@@ -3221,7 +3233,7 @@
     <row r="132">
       <c r="B132" s="31" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ CB-9 7890</t>
+          <t>Материя 80мл CB-9 7890</t>
         </is>
       </c>
       <c r="C132" s="36" t="n">
@@ -3240,7 +3252,7 @@
     <row r="133">
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ GR-12 0726</t>
+          <t>Материя 80мл GR-12 0726</t>
         </is>
       </c>
       <c r="C133" s="10" t="n">
@@ -3259,7 +3271,7 @@
     <row r="134">
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ MA-10 0672</t>
+          <t>Материя 80мл MA-10 0672</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
@@ -3278,7 +3290,7 @@
     <row r="135">
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ MT-8 8262/0-MT-8</t>
+          <t>Материя 80мл MT-8 8262/0-MT-8</t>
         </is>
       </c>
       <c r="C135" s="10" t="n">
@@ -3297,7 +3309,7 @@
     <row r="136">
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ P-12 8682</t>
+          <t>Материя 80мл P-12 8682</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
@@ -3316,7 +3328,7 @@
     <row r="137">
       <c r="B137" s="31" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ V-8 8637</t>
+          <t>Материя 80мл V-8 8637</t>
         </is>
       </c>
       <c r="C137" s="36" t="n">
@@ -3335,7 +3347,7 @@
     <row r="138">
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ WB-10 8057/0-WB-10</t>
+          <t>Материя 80мл WB-10 8057/0-WB-10</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
@@ -3354,7 +3366,7 @@
     <row r="139">
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ WB-6 8019</t>
+          <t>Материя 80мл WB-6 8019</t>
         </is>
       </c>
       <c r="C139" s="10" t="n">
@@ -3373,7 +3385,7 @@
     <row r="140">
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ WB-7 8026</t>
+          <t>Материя 80мл WB-7 8026</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
@@ -3392,7 +3404,7 @@
     <row r="141">
       <c r="B141" s="31" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ WB-8 8033</t>
+          <t>Материя 80мл WB-8 8033</t>
         </is>
       </c>
       <c r="C141" s="36" t="n">
@@ -3411,7 +3423,7 @@
     <row r="142">
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ WB-9 8040/0-WB-9</t>
+          <t>Материя 80мл WB-9 8040/0-WB-9</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
@@ -3430,7 +3442,7 @@
     <row r="143">
       <c r="B143" s="31" t="inlineStr">
         <is>
-          <t>Краска д/волос тон µ A-8 9283</t>
+          <t>Материя µ 80мл A-8 9283</t>
         </is>
       </c>
       <c r="C143" s="36" t="n">
@@ -3449,7 +3461,7 @@
     <row r="144">
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос тон µ Be-10 9023/mB-10</t>
+          <t>Материя µ 80мл Be-10 9023/mB-10</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
@@ -3468,7 +3480,7 @@
     <row r="145">
       <c r="B145" s="31" t="inlineStr">
         <is>
-          <t>Краска д/волос тон µ M-6 9221/mM-6</t>
+          <t>Материя µ 80мл M-6 9221/mM-6</t>
         </is>
       </c>
       <c r="C145" s="36" t="n">
@@ -3487,7 +3499,7 @@
     <row r="146">
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос тон µ MT-6 9085/mMT-6</t>
+          <t>Материя µ 80мл MT-6 9085/mMT-6</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
@@ -3506,7 +3518,7 @@
     <row r="147">
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос тон µ P-10 9382</t>
+          <t>Материя µ 80мл P-10 9382</t>
         </is>
       </c>
       <c r="C147" s="10" t="n">
@@ -3525,7 +3537,7 @@
     <row r="148">
       <c r="B148" s="31" t="inlineStr">
         <is>
-          <t>Краска д/волос тон µ P-8 80 г 9375лп</t>
+          <t>Материя µ 80мл P-8 80г 9375лп</t>
         </is>
       </c>
       <c r="C148" s="36" t="n">
@@ -3544,7 +3556,7 @@
     <row r="149">
       <c r="B149" s="31" t="inlineStr">
         <is>
-          <t>Краска д/волос тон µ Pe-8 9061</t>
+          <t>Материя µ 80мл Pe-8 9061</t>
         </is>
       </c>
       <c r="C149" s="36" t="n">
@@ -3563,7 +3575,7 @@
     <row r="150">
       <c r="B150" s="31" t="inlineStr">
         <is>
-          <t>Краска д/волос тон µ WB-5 8880/mWB-5</t>
+          <t>Материя µ 80мл WB-5 8880/mWB-5</t>
         </is>
       </c>
       <c r="C150" s="36" t="n">
@@ -3582,7 +3594,7 @@
     <row r="151">
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос тон µ WB-8 8910</t>
+          <t>Материя µ 80мл WB-8 8910</t>
         </is>
       </c>
       <c r="C151" s="10" t="n">
@@ -3601,7 +3613,7 @@
     <row r="152">
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>Крем д/волос IAUSERUM CREAM 200мл 5420</t>
+          <t>Крем для волос IAUSERUM CREAM 200мл 5420</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
@@ -3620,7 +3632,7 @@
     <row r="153">
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>Крем д/укладки волос TRIE TUNER CREAM O 95мл. 1391</t>
+          <t>Крем для укладки волос TRIE TUNER CREAM O 95мл 1391</t>
         </is>
       </c>
       <c r="C153" s="10" t="n">
@@ -3639,7 +3651,7 @@
     <row r="154">
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>Крем защитный для кожи головы PRE SKIN CREAM 150 г 7784</t>
+          <t>Крем защитный для кожи головы PRE SKIN CREAM 150г 7784</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
@@ -3696,7 +3708,7 @@
     <row r="157">
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>Крем интенс. д/укр. волос IAU CELL CARE 3S 1000мл 5239</t>
+          <t>Крем интенсивный для укрнпления волос IAU CELL CARE 3S 1000мл 5239</t>
         </is>
       </c>
       <c r="C157" s="10" t="n">
@@ -3715,7 +3727,7 @@
     <row r="158">
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>Крем интенс. д/укр. волос IAU CELL CARE 3S 500мл 5222</t>
+          <t>Крем интенсивный для укрнпления волос IAU CELL CARE 3S 500мл 5222</t>
         </is>
       </c>
       <c r="C158" s="10" t="n">
@@ -3734,7 +3746,7 @@
     <row r="159">
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>Крем фиксирующий для выпрямления. Шаг2 Rufor 2-800g 2827</t>
+          <t>Крем фиксирующий для выпрямления 2й-шаг Rufor 800мл 2827</t>
         </is>
       </c>
       <c r="C159" s="10" t="n">
@@ -3753,7 +3765,7 @@
     <row r="160">
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>Крем-фиксатор Rufor Chemical shower 800g 2834</t>
+          <t>Крем-фиксатор Rufor Chemical shower 800мл 2834</t>
         </is>
       </c>
       <c r="C160" s="10" t="n">
@@ -3772,7 +3784,7 @@
     <row r="161" ht="22.5" customHeight="1">
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>Маска "Proedit Bounce Fit +" восстанавливающая+объем для тонких и сухих, 1000 мл. 3488</t>
+          <t>Маска "Proedit Bounce Fit +" восстанавливающая + объём для тонких и сухих 1000мл 3488</t>
         </is>
       </c>
       <c r="C161" s="10" t="n">
@@ -3791,7 +3803,7 @@
     <row r="162" ht="22.5" customHeight="1">
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>Маска "Proedit Bounce Fit +" восстанавливающая+объем для тонких и сухих, 250 мл. 3174</t>
+          <t>Маска "Proedit Bounce Fit +" восстанавливающая + объём для тонких и сухих 250мл 3174</t>
         </is>
       </c>
       <c r="C162" s="10" t="n">
@@ -3810,7 +3822,7 @@
     <row r="163">
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>Маска "PBF" восст. д/тонких и сухих, 1000 мл. 3471</t>
+          <t>Маска "Proedit Bounce Fit" восстановливающая для тонких и сухих 1000мл 3471</t>
         </is>
       </c>
       <c r="C163" s="10" t="n">
@@ -3829,7 +3841,7 @@
     <row r="164" ht="22.5" customHeight="1">
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t>Маска "Proedit Bounce Fit" восстанавливающая для тонких и сухих, 250 мл. 3136</t>
+          <t>Маска "Proedit Bounce Fit" восстанавливающая для тонких и сухих 250мл 3136</t>
         </is>
       </c>
       <c r="C164" s="10" t="n">
@@ -3848,7 +3860,7 @@
     <row r="165" ht="22.5" customHeight="1">
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>Маска "Wheat Protein" рисовый протейн, восстанавливающая для тонких, 140 гр.!! 4959-1422</t>
+          <t>Маска "Wheat Protein" рисовый протейн, восстанавливающая для тонких 140мл 4959-1422</t>
         </is>
       </c>
       <c r="C165" s="10" t="n">
@@ -3867,7 +3879,7 @@
     <row r="166">
       <c r="B166" s="7" t="inlineStr">
         <is>
-          <t>Масло для восстановления волос Viege Oil 90 мл. 5802</t>
+          <t>Масло для восстановления волос Viege Oil 90мл 5802</t>
         </is>
       </c>
       <c r="C166" s="10" t="n">
@@ -3886,7 +3898,7 @@
     <row r="167">
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>Мусс для волос и кожи головы очищающий PHFC 250 г. 4058</t>
+          <t>Мусс для волос и кожи головы очищающий PHFC 250г 4058</t>
         </is>
       </c>
       <c r="C167" s="10" t="n">
@@ -3905,7 +3917,7 @@
     <row r="168">
       <c r="B168" s="7" t="inlineStr">
         <is>
-          <t>Мусс клеточный увлажняющий IAU CELL CARE (1) 500 мл. 5185</t>
+          <t>Мусс клеточный увлажняющий IAU CELL CARE (1) 500мл 5185</t>
         </is>
       </c>
       <c r="C168" s="10" t="n">
@@ -4000,7 +4012,7 @@
     <row r="173">
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>Сыворотка протеиновая IAU Cell Care 2, 500 мл 5215</t>
+          <t>Сыворотка протеиновая IAU Cell Care 2 500мл 5215</t>
         </is>
       </c>
       <c r="C173" s="10" t="n">
@@ -4019,7 +4031,7 @@
     <row r="174" ht="22.5" customHeight="1">
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t>Шампунь "Proedit Bounce Fit" восстанавливающий для тонких и сухих волос, 1000 мл. 3433</t>
+          <t>Шампунь "Proedit Bounce Fit" восстанавливающий для тонких и сухих волос 1000мл 3433</t>
         </is>
       </c>
       <c r="C174" s="10" t="n">
@@ -4038,7 +4050,7 @@
     <row r="175" ht="22.5" customHeight="1">
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>Шампунь "Proedit Bounce Fit" восстанавливающий для тонких и сухих волос, 300 мл. 2979</t>
+          <t>Шампунь "Proedit Bounce Fit" восстанавливающий для тонких и сухих волос 300мл 2979</t>
         </is>
       </c>
       <c r="C175" s="10" t="n">
@@ -4057,7 +4069,7 @@
     <row r="176" ht="22.5" customHeight="1">
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>Шампунь "Proedit Soft Fit" увлажняющий для жестких и сухих, 1000 мл. 3457</t>
+          <t>Шампунь "Proedit Soft Fit" увлажняющий для жестких и сухих 1000мл 3457</t>
         </is>
       </c>
       <c r="C176" s="10" t="n">
@@ -4076,7 +4088,7 @@
     <row r="177">
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>Шампунь увл. IAU SERUM Cleansing 200 мл. 5383</t>
+          <t>Шампунь увлажняющий IAU SERUM Cleansing 200мл 5383</t>
         </is>
       </c>
       <c r="C177" s="10" t="n">
@@ -4095,7 +4107,7 @@
     <row r="178">
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>Эссенция "Sleek" разглаживающее масло, 100 мл. 4669-3891</t>
+          <t>Эссенция "Sleek" разглаживающее масло 100мл 4669-3891</t>
         </is>
       </c>
       <c r="C178" s="10" t="n">
@@ -4117,15 +4129,15 @@
           <t>LEVISSIME</t>
         </is>
       </c>
-      <c r="C179" s="16" t="n"/>
+      <c r="C179" s="43" t="n"/>
       <c r="D179" s="24" t="n"/>
-      <c r="E179" s="25" t="n"/>
-      <c r="F179" s="26" t="n"/>
+      <c r="E179" s="24" t="n"/>
+      <c r="F179" s="44" t="n"/>
     </row>
     <row r="180">
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>Краска для бровей и ресниц 1 черный 15 мл 1</t>
+          <t>Краска для бровей и ресниц 1 черный 15мл 1</t>
         </is>
       </c>
       <c r="C180" s="8" t="n">
@@ -4144,7 +4156,7 @@
     <row r="181">
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>Краска для бровей и ресниц 3/7 коричневый 15 мл 3-7</t>
+          <t>Краска для бровей и ресниц 3/7 коричневый 15мл 3-7</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
@@ -4166,10 +4178,10 @@
           <t>LONDA</t>
         </is>
       </c>
-      <c r="C182" s="16" t="n"/>
+      <c r="C182" s="43" t="n"/>
       <c r="D182" s="24" t="n"/>
-      <c r="E182" s="25" t="n"/>
-      <c r="F182" s="26" t="n"/>
+      <c r="E182" s="24" t="n"/>
+      <c r="F182" s="44" t="n"/>
     </row>
     <row r="183">
       <c r="B183" s="31" t="inlineStr">
@@ -4231,7 +4243,7 @@
     <row r="186">
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 10-38 яркий блонд золот-жемч 01038</t>
+          <t>LC крем-краска 10-38 яркий блонд золотисто-жемч 01038</t>
         </is>
       </c>
       <c r="C186" s="8" t="n">
@@ -4421,7 +4433,7 @@
     <row r="196">
       <c r="B196" s="31" t="inlineStr">
         <is>
-          <t>LC крем-краска 12-96 спец. блондин сандрэ фиолет. 01296</t>
+          <t>LC крем-краска 12-96 специальный блондин сандрэ фиолетовый 01296</t>
         </is>
       </c>
       <c r="C196" s="32" t="n">
@@ -4668,7 +4680,7 @@
     <row r="209">
       <c r="B209" s="31" t="inlineStr">
         <is>
-          <t>LC крем-краска 5-07 св. шатен натурально-коричневый 0507</t>
+          <t>LC крем-краска 5-07 светлый шатен натурально-коричневый 0507</t>
         </is>
       </c>
       <c r="C209" s="32" t="n">
@@ -4706,7 +4718,7 @@
     <row r="211">
       <c r="B211" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 5-37 св. шатен золот-коричнев 0537</t>
+          <t>LC крем-краска 5-37 светлый шатен золотисто-коричневый 0537</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
@@ -4725,7 +4737,7 @@
     <row r="212">
       <c r="B212" s="31" t="inlineStr">
         <is>
-          <t>LC крем-краска 5-7 светл шатен коричнев 057</t>
+          <t>LC крем-краска 5-7 светл шатен коричневый 057</t>
         </is>
       </c>
       <c r="C212" s="32" t="n">
@@ -4763,7 +4775,7 @@
     <row r="214">
       <c r="B214" s="31" t="inlineStr">
         <is>
-          <t>LC крем-краска 5-74 св.шатен коричнево-медн. 0574</t>
+          <t>LC крем-краска 5-74 светлый шатен коричнево-медный 0574</t>
         </is>
       </c>
       <c r="C214" s="32" t="n">
@@ -4782,7 +4794,7 @@
     <row r="215">
       <c r="B215" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 5-77 св.шатен интенсивно-коричневый 0577</t>
+          <t>LC крем-краска 5-77 светлый шатен интенсивно-коричневый 0577</t>
         </is>
       </c>
       <c r="C215" s="8" t="n">
@@ -4896,7 +4908,7 @@
     <row r="221">
       <c r="B221" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 6-3 темн. блонд. золот 063</t>
+          <t>LC крем-краска 6-3 тёмный блонд золотистый 063</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
@@ -5523,7 +5535,7 @@
     <row r="254">
       <c r="B254" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 8-07 св. блонд натурально-коричневый 0807</t>
+          <t>LC крем-краска 8-07 светлый блонд натурально-коричневый 0807</t>
         </is>
       </c>
       <c r="C254" s="8" t="n">
@@ -5542,7 +5554,7 @@
     <row r="255">
       <c r="B255" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 8-3 светл. блонд золотистый 083</t>
+          <t>LC крем-краска 8-3 светлый блонд золотистый 083</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
@@ -5561,7 +5573,7 @@
     <row r="256">
       <c r="B256" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 8-38 св. блонд золот-жемчужный 0838</t>
+          <t>LC крем-краска 8-38 светлый блонд золотисто-жемчужный 0838</t>
         </is>
       </c>
       <c r="C256" s="8" t="n">
@@ -5580,7 +5592,7 @@
     <row r="257">
       <c r="B257" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 8-4 св. блонд медный 084</t>
+          <t>LC крем-краска 8-4 светлый блонд медный 084</t>
         </is>
       </c>
       <c r="C257" s="8" t="n">
@@ -5618,7 +5630,7 @@
     <row r="259">
       <c r="B259" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 8-43 св. блонд медно-золотистый 0843</t>
+          <t>LC крем-краска 8-43 светлый блонд медно-золотистый 0843</t>
         </is>
       </c>
       <c r="C259" s="8" t="n">
@@ -5732,7 +5744,7 @@
     <row r="265">
       <c r="B265" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска  8-71 св. блонд корич-пепельный 0871</t>
+          <t>LC крем-краска 8-71 светлый блонд корич-пепельный 0871</t>
         </is>
       </c>
       <c r="C265" s="8" t="n">
@@ -5827,7 +5839,7 @@
     <row r="270">
       <c r="B270" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 9-0 оч. светл. блонд 090</t>
+          <t>LC крем-краска 9-0 очень светлый блонд 090</t>
         </is>
       </c>
       <c r="C270" s="8" t="n">
@@ -5846,7 +5858,7 @@
     <row r="271">
       <c r="B271" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 9-1 оч. светл. блонд пепельный 091</t>
+          <t>LC крем-краска 9-1 очень светлый блонд пепельный 091</t>
         </is>
       </c>
       <c r="C271" s="8" t="n">
@@ -5903,7 +5915,7 @@
     <row r="274">
       <c r="B274" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 9-3 оч. светл. блонд золотистый 093</t>
+          <t>LC крем-краска 9-3 очень светлый блонд золотистый 093</t>
         </is>
       </c>
       <c r="C274" s="8" t="n">
@@ -5941,7 +5953,7 @@
     <row r="276">
       <c r="B276" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 9-38 оч. св. блонд золот-перламут 0938</t>
+          <t>LC крем-краска 9-38 очень светлый блонд золотисто-перламут 0938</t>
         </is>
       </c>
       <c r="C276" s="8" t="n">
@@ -5960,7 +5972,7 @@
     <row r="277">
       <c r="B277" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 9-65 оч.светлый блондин фиол.-красный 0965</t>
+          <t>LC крем-краска 9-65 очень светлый блондин фиолетовый -красный 0965</t>
         </is>
       </c>
       <c r="C277" s="8" t="n">
@@ -5998,7 +6010,7 @@
     <row r="279">
       <c r="B279" s="7" t="inlineStr">
         <is>
-          <t>LC крем-краска 9/ интенсивный оч. светл. блонд (теплый) 0/9</t>
+          <t>LC крем-краска 9/ интенсивный очень светлый блонд (теплый) 0/9</t>
         </is>
       </c>
       <c r="C279" s="8" t="n">
@@ -6112,7 +6124,7 @@
     <row r="285">
       <c r="B285" s="7" t="inlineStr">
         <is>
-          <t>LC тонер /07 60 мл. 07</t>
+          <t>LC тонер /07 60мл 07</t>
         </is>
       </c>
       <c r="C285" s="8" t="n">
@@ -6131,7 +6143,7 @@
     <row r="286">
       <c r="B286" s="7" t="inlineStr">
         <is>
-          <t>LC тонер /1 60 мл. 1</t>
+          <t>LC тонер /1 60мл 1</t>
         </is>
       </c>
       <c r="C286" s="8" t="n">
@@ -6150,7 +6162,7 @@
     <row r="287">
       <c r="B287" s="7" t="inlineStr">
         <is>
-          <t>LC тонер /19 60 мл. 19</t>
+          <t>LC тонер /19 60мл 19</t>
         </is>
       </c>
       <c r="C287" s="8" t="n">
@@ -6169,7 +6181,7 @@
     <row r="288">
       <c r="B288" s="7" t="inlineStr">
         <is>
-          <t>LC тонер /69 60 мл. 69</t>
+          <t>LC тонер /69 60мл 69</t>
         </is>
       </c>
       <c r="C288" s="8" t="n">
@@ -6340,7 +6352,7 @@
     <row r="297">
       <c r="B297" s="7" t="inlineStr">
         <is>
-          <t>LC тонирование 5/71 св. шатен корич-пепельный 0-571</t>
+          <t>LC тонирование 5/71 светлый шатен корич-пепельный 0-571</t>
         </is>
       </c>
       <c r="C297" s="8" t="n">
@@ -6378,7 +6390,7 @@
     <row r="299">
       <c r="B299" s="7" t="inlineStr">
         <is>
-          <t>LC тонирование 6/37 тёмн блонд золот-коричневый 0-637</t>
+          <t>LC тонирование 6/37 тёмн блонд золотисто-коричневый 0-637</t>
         </is>
       </c>
       <c r="C299" s="8" t="n">
@@ -6473,7 +6485,7 @@
     <row r="304">
       <c r="B304" s="7" t="inlineStr">
         <is>
-          <t>LC тонирование 6/77 тёмн блонд интенсив коричнев 0-677</t>
+          <t>LC тонирование 6/77 тёмн блонд интенсив коричневый 0-677</t>
         </is>
       </c>
       <c r="C304" s="8" t="n">
@@ -6568,7 +6580,7 @@
     <row r="309">
       <c r="B309" s="7" t="inlineStr">
         <is>
-          <t>LC тонирование 8/43 светлый блонд медн.зол 0-843</t>
+          <t>LC тонирование 8/43 светлый блонд медно-золотистый 0-843</t>
         </is>
       </c>
       <c r="C309" s="8" t="n">
@@ -6587,7 +6599,7 @@
     <row r="310">
       <c r="B310" s="7" t="inlineStr">
         <is>
-          <t>LC тонирование 8/71 св. блонд корич-пепельный 0-871</t>
+          <t>LC тонирование 8/71 светлый блонд корич-пепельный 0-871</t>
         </is>
       </c>
       <c r="C310" s="8" t="n">
@@ -6663,7 +6675,7 @@
     <row r="314">
       <c r="B314" s="31" t="inlineStr">
         <is>
-          <t>LC тонирование 9/36 оч. св. блонд золот-фиолетов 0-936</t>
+          <t>LC тонирование 9/36 очень светлый блонд золотисто-фиолетов 0-936</t>
         </is>
       </c>
       <c r="C314" s="32" t="n">
@@ -6682,7 +6694,7 @@
     <row r="315">
       <c r="B315" s="7" t="inlineStr">
         <is>
-          <t>LC тонирование 9/73 оч. св. блонд коричнево-зол 0-973</t>
+          <t>LC тонирование 9/73 очень светлый блонд коричнево-золотистый 0-973</t>
         </is>
       </c>
       <c r="C315" s="8" t="n">
@@ -6739,7 +6751,7 @@
     <row r="318">
       <c r="B318" s="7" t="inlineStr">
         <is>
-          <t>LC тонирование экстра 4/07 шатен нат.кор. 0-407</t>
+          <t>LC тонирование экстра 4/07 шатен натуральный коричневый 0-407</t>
         </is>
       </c>
       <c r="C318" s="8" t="n">
@@ -6758,7 +6770,7 @@
     <row r="319">
       <c r="B319" s="7" t="inlineStr">
         <is>
-          <t>LC тонирование экстра 5/07 св.шатен нат.кор. 0-507</t>
+          <t>LC тонирование экстра 5/07 светлый шатен натуральный коричневый 0-507</t>
         </is>
       </c>
       <c r="C319" s="8" t="n">
@@ -6815,7 +6827,7 @@
     <row r="322">
       <c r="B322" s="7" t="inlineStr">
         <is>
-          <t>Блондоран препар. д/интенс. освет. волос 500г 642</t>
+          <t>Блондоран осветляющая пудра 500г 642</t>
         </is>
       </c>
       <c r="C322" s="10" t="n">
@@ -6853,7 +6865,7 @@
     <row r="324">
       <c r="B324" s="31" t="inlineStr">
         <is>
-          <t>Кондиционер д/окрашенных волос 250мл 4764/10560</t>
+          <t>Кондиционер для окрашенных волос 250мл 4764/10560</t>
         </is>
       </c>
       <c r="C324" s="32" t="n">
@@ -6872,7 +6884,7 @@
     <row r="325">
       <c r="B325" s="31" t="inlineStr">
         <is>
-          <t>Кондиционер д/поврежденных волос 1000мл 4956/10566</t>
+          <t>Кондиционер для поврежденных волос 1000мл 4956/10566</t>
         </is>
       </c>
       <c r="C325" s="36" t="n">
@@ -6891,7 +6903,7 @@
     <row r="326">
       <c r="B326" s="31" t="inlineStr">
         <is>
-          <t>Кондиционер д/поврежденных волос 250мл 4955/10567</t>
+          <t>Кондиционер для поврежденных волос 250мл 4955/10567</t>
         </is>
       </c>
       <c r="C326" s="32" t="n">
@@ -6948,7 +6960,7 @@
     <row r="329" ht="22.5" customHeight="1">
       <c r="B329" s="31" t="inlineStr">
         <is>
-          <t>Кондиционер-бальзам д/поврежденных волос НЕСМЫВАЕМЫЙ 250мл 4961/10568</t>
+          <t>Кондиционер-бальзам для поврежденных волос НЕСМЫВАЕМЫЙ 250мл 4961/10568</t>
         </is>
       </c>
       <c r="C329" s="32" t="n">
@@ -6967,7 +6979,7 @@
     <row r="330" ht="22.5" customHeight="1">
       <c r="B330" s="31" t="inlineStr">
         <is>
-          <t>Лак д/волос №1 Эластич. Фикс. 500мл FLEXIBLE LAYER UP 4736/12472</t>
+          <t>Лак для волос №1 эластичной фиксации 500мл FLEXIBLE LAYER UP 4736/12472</t>
         </is>
       </c>
       <c r="C330" s="32" t="n">
@@ -6986,7 +6998,7 @@
     <row r="331">
       <c r="B331" s="31" t="inlineStr">
         <is>
-          <t>Лак д/волос №2 СФ 300мл STRONG FIX IT 5376/12467</t>
+          <t>Лак для волос №2 сильной фиксации 300мл STRONG FIX IT 5376/12467</t>
         </is>
       </c>
       <c r="C331" s="32" t="n">
@@ -7005,7 +7017,7 @@
     <row r="332">
       <c r="B332" s="31" t="inlineStr">
         <is>
-          <t>Лак д/волос №2 СФ 500мл STRONG FIX IT 5353/12468/10476</t>
+          <t>Лак для волос №2 сильной фиксации 500мл STRONG FIX IT 5353/12468/10476</t>
         </is>
       </c>
       <c r="C332" s="32" t="n">
@@ -7024,7 +7036,7 @@
     <row r="333">
       <c r="B333" s="31" t="inlineStr">
         <is>
-          <t>Лак д/волос №3 Экстрасильной Фикс. 500мл START OFF 12470</t>
+          <t>Лак для волос №3 экстрасильной фиксации 500мл START OFF 12470</t>
         </is>
       </c>
       <c r="C333" s="32" t="n">
@@ -7043,7 +7055,7 @@
     <row r="334" ht="22.5" customHeight="1">
       <c r="B334" s="31" t="inlineStr">
         <is>
-          <t>Лак д/волос №4 Экстремальной Фиксации 250мл EXTREME STRONG LOCK IT 10645/12465</t>
+          <t>Лак для волос №4 экстремальной фиксации 250мл EXTREME STRONG LOCK IT 10645/12465</t>
         </is>
       </c>
       <c r="C334" s="32" t="n">
@@ -7062,7 +7074,7 @@
     <row r="335" ht="22.5" customHeight="1">
       <c r="B335" s="31" t="inlineStr">
         <is>
-          <t>Лак д/волос №4 Экстремальной Фиксации 500мл EXTREME STRONG LOCK IT 5274/12466</t>
+          <t>Лак для волос №4 экстремальной фиксации 500мл EXTREME STRONG LOCK IT 5274/12466</t>
         </is>
       </c>
       <c r="C335" s="32" t="n">
@@ -7081,7 +7093,7 @@
     <row r="336">
       <c r="B336" s="31" t="inlineStr">
         <is>
-          <t>Лосьон теплозащ.д/обема НФ 150мл новая PROTECT IT 5250-10458</t>
+          <t>Лосьон теплозащитный для объёма нормальной фиксации 150мл новая PROTECT IT 5250-10458</t>
         </is>
       </c>
       <c r="C336" s="32" t="n">
@@ -7100,7 +7112,7 @@
     <row r="337">
       <c r="B337" s="7" t="inlineStr">
         <is>
-          <t>маска интенс. д/поврежденных волос 200 мл 4953/10570</t>
+          <t>маска интенсивная для поврежденных волос 200мл 4953/10570</t>
         </is>
       </c>
       <c r="C337" s="8" t="n">
@@ -7119,7 +7131,7 @@
     <row r="338">
       <c r="B338" s="7" t="inlineStr">
         <is>
-          <t>маска интенс. д/сохр. цвета и блеска 200 мл. 4928/10563</t>
+          <t>маска интенсивная для сохранения цвета и блеска 200мл 4928/10563</t>
         </is>
       </c>
       <c r="C338" s="8" t="n">
@@ -7138,7 +7150,7 @@
     <row r="339">
       <c r="B339" s="7" t="inlineStr">
         <is>
-          <t>маска интенс. увлажняющая волос 200 мл 4939/10587</t>
+          <t>маска интенсивная увлажняющая волос 200мл 4939/10587</t>
         </is>
       </c>
       <c r="C339" s="8" t="n">
@@ -7157,7 +7169,7 @@
     <row r="340">
       <c r="B340" s="31" t="inlineStr">
         <is>
-          <t>Масло VELVET OIL с аргановым маслом 100 мл 7543</t>
+          <t>Масло VELVET OIL с аргановым маслом 100мл 7543</t>
         </is>
       </c>
       <c r="C340" s="32" t="n">
@@ -7176,7 +7188,7 @@
     <row r="341">
       <c r="B341" s="7" t="inlineStr">
         <is>
-          <t>Мусс д/создания прикорневого объема СФ 200 мл LIFT IT 5301-10459</t>
+          <t>Мусс для создания прикорневого объёма сильной фиксации 200мл LIFT IT 5301-10459</t>
         </is>
       </c>
       <c r="C341" s="8" t="n">
@@ -7195,7 +7207,7 @@
     <row r="342">
       <c r="B342" s="31" t="inlineStr">
         <is>
-          <t>L-Color окислительная эмульсия 1,9% 1000 мл 914</t>
+          <t>L-Color окислительная эмульсия 1,9% 1000мл 914</t>
         </is>
       </c>
       <c r="C342" s="32" t="n">
@@ -7214,7 +7226,7 @@
     <row r="343">
       <c r="B343" s="31" t="inlineStr">
         <is>
-          <t>окислительная эмульсия 1,9% 60 мл 7371</t>
+          <t>L-Color окислительная эмульсия 1,9% 60мл 7371</t>
         </is>
       </c>
       <c r="C343" s="32" t="n">
@@ -7233,7 +7245,7 @@
     <row r="344">
       <c r="B344" s="31" t="inlineStr">
         <is>
-          <t>L-Color окислительная эмульсия 12% 1000 мл 919</t>
+          <t>L-Color окислительная эмульсия 12% 1000мл 919</t>
         </is>
       </c>
       <c r="C344" s="32" t="n">
@@ -7252,7 +7264,7 @@
     <row r="345">
       <c r="B345" s="7" t="inlineStr">
         <is>
-          <t>L-Color окислительная эмульсия 3% 1000 мл 916</t>
+          <t>L-Color окислительная эмульсия 3% 1000мл 916</t>
         </is>
       </c>
       <c r="C345" s="8" t="n">
@@ -7271,7 +7283,7 @@
     <row r="346">
       <c r="B346" s="31" t="inlineStr">
         <is>
-          <t>L-Color окислительная эмульсия 4% 1000 мл. 915</t>
+          <t>L-Color окислительная эмульсия 4% 1000мл 915</t>
         </is>
       </c>
       <c r="C346" s="32" t="n">
@@ -7290,7 +7302,7 @@
     <row r="347">
       <c r="B347" s="7" t="inlineStr">
         <is>
-          <t>L-Color окислительная эмульсия 6% 1000 мл 917</t>
+          <t>L-Color окислительная эмульсия 6% 1000мл 917</t>
         </is>
       </c>
       <c r="C347" s="8" t="n">
@@ -7309,7 +7321,7 @@
     <row r="348">
       <c r="B348" s="31" t="inlineStr">
         <is>
-          <t>Окислительная эмульсия 6% 60 мл 7374</t>
+          <t>L-Color окислительная эмульсия 6% 60мл 7374</t>
         </is>
       </c>
       <c r="C348" s="32" t="n">
@@ -7328,7 +7340,7 @@
     <row r="349">
       <c r="B349" s="7" t="inlineStr">
         <is>
-          <t>L-Color окислительная эмульсия 9% 1000 мл 918 NEW</t>
+          <t>L-Color окислительная эмульсия 9% 1000мл 918</t>
         </is>
       </c>
       <c r="C349" s="8" t="n">
@@ -7347,7 +7359,7 @@
     <row r="350">
       <c r="B350" s="31" t="inlineStr">
         <is>
-          <t>Окислительная эмульсия 9% 60 мл 7375</t>
+          <t>L-Color окислительная эмульсия 9% 60мл 7375</t>
         </is>
       </c>
       <c r="C350" s="32" t="n">
@@ -7366,7 +7378,7 @@
     <row r="351">
       <c r="B351" s="31" t="inlineStr">
         <is>
-          <t>Пена д/укладки НФ 200 мл ENHANCE IT 5304-10457</t>
+          <t>Пена для укладки нормальной фиксации 200мл ENHANCE IT 5304-10457</t>
         </is>
       </c>
       <c r="C351" s="32" t="n">
@@ -7385,7 +7397,7 @@
     <row r="352">
       <c r="B352" s="31" t="inlineStr">
         <is>
-          <t>Пена д/укладки СФ 250 мл EXPAND IT 5297-10460</t>
+          <t>Пена для укладки сильной фиксации 250мл EXPAND IT 5297-10460</t>
         </is>
       </c>
       <c r="C352" s="32" t="n">
@@ -7423,7 +7435,7 @@
     <row r="354" ht="22.5" customHeight="1">
       <c r="B354" s="31" t="inlineStr">
         <is>
-          <t>Ср-во FIBER INFUSION восстанавливающий с кератином 200 мл 5086</t>
+          <t>Средство (маска) FIBER INFUSION восстанавливающее с кератином 200мл 5086</t>
         </is>
       </c>
       <c r="C354" s="36" t="n">
@@ -7442,7 +7454,7 @@
     <row r="355">
       <c r="B355" s="7" t="inlineStr">
         <is>
-          <t>Ср-во VELVET OIL с аргановым маслом 200мл 1251</t>
+          <t>Средство (маска) VELVET OIL с аргановым маслом 200мл 1251</t>
         </is>
       </c>
       <c r="C355" s="8" t="n">
@@ -7461,7 +7473,7 @@
     <row r="356">
       <c r="B356" s="31" t="inlineStr">
         <is>
-          <t>Ср-во VELVET OIL с аргановым маслом 750мл 1252</t>
+          <t>Средство (маска) VELVET OIL с аргановым маслом 750мл 1252</t>
         </is>
       </c>
       <c r="C356" s="36" t="n">
@@ -7480,7 +7492,7 @@
     <row r="357" ht="22.5" customHeight="1">
       <c r="B357" s="31" t="inlineStr">
         <is>
-          <t>ср-во ВОССТАНАВЛИВАЮЩЕЕ д/поврежденных волос 750 мл 4952/10569</t>
+          <t>Средство (маска) восстанавливающее для поврежденных волос 750мл 4952/10569</t>
         </is>
       </c>
       <c r="C357" s="36" t="n">
@@ -7499,7 +7511,7 @@
     <row r="358">
       <c r="B358" s="31" t="inlineStr">
         <is>
-          <t>Стабилизатор д/сохранения цвета 1000 мл 4927/10562</t>
+          <t>Стабилизатор для сохранения цвета 1000мл 4927/10562</t>
         </is>
       </c>
       <c r="C358" s="36" t="n">
@@ -7518,7 +7530,7 @@
     <row r="359" ht="22.5" customHeight="1">
       <c r="B359" s="31" t="inlineStr">
         <is>
-          <t>Шампунь FIBER INFUSION восстанавливающий с кератином 1000 мл. 5094</t>
+          <t>Шампунь FIBER INFUSION восстанавливающий с кератином 1000мл 5094</t>
         </is>
       </c>
       <c r="C359" s="36" t="n">
@@ -7537,7 +7549,7 @@
     <row r="360" ht="22.5" customHeight="1">
       <c r="B360" s="31" t="inlineStr">
         <is>
-          <t>Шампунь FIBER INFUSION восстанавливающий с кератином 250 мл. 5084</t>
+          <t>Шампунь FIBER INFUSION восстанавливающий с кератином 250мл 5084</t>
         </is>
       </c>
       <c r="C360" s="32" t="n">
@@ -7556,7 +7568,7 @@
     <row r="361">
       <c r="B361" s="31" t="inlineStr">
         <is>
-          <t>Шампунь VELVET OIL с аргановым маслом 1000 мл. 1266</t>
+          <t>Шампунь VELVET OIL с аргановым маслом 1000мл 1266</t>
         </is>
       </c>
       <c r="C361" s="36" t="n">
@@ -7575,7 +7587,7 @@
     <row r="362">
       <c r="B362" s="31" t="inlineStr">
         <is>
-          <t>Шампунь VELVET OIL с аргановым маслом 250 мл. 1248</t>
+          <t>Шампунь VELVET OIL с аргановым маслом 250мл 1248</t>
         </is>
       </c>
       <c r="C362" s="32" t="n">
@@ -7594,7 +7606,7 @@
     <row r="363">
       <c r="B363" s="31" t="inlineStr">
         <is>
-          <t>Шампунь д/объма 1000 мл 4943/10588</t>
+          <t>Шампунь для объёма 1000мл 4943/10588</t>
         </is>
       </c>
       <c r="C363" s="36" t="n">
@@ -7613,7 +7625,7 @@
     <row r="364">
       <c r="B364" s="31" t="inlineStr">
         <is>
-          <t>Шампунь д/поврежденных волос 250 мл 4958/10565</t>
+          <t>Шампунь для поврежденных волос 250мл 4958/10565</t>
         </is>
       </c>
       <c r="C364" s="32" t="n">
@@ -7632,7 +7644,7 @@
     <row r="365">
       <c r="B365" s="31" t="inlineStr">
         <is>
-          <t>Шампунь д/сохранения цвета и блеска 250 мл 4934/10558</t>
+          <t>Шампунь для сохранения цвета и блеска 250мл 4934/10558</t>
         </is>
       </c>
       <c r="C365" s="32" t="n">
@@ -7651,7 +7663,7 @@
     <row r="366">
       <c r="B366" s="31" t="inlineStr">
         <is>
-          <t>Шампунь против перхоти 250 мл 4924/10573</t>
+          <t>Шампунь против перхоти 250мл 4924/10573</t>
         </is>
       </c>
       <c r="C366" s="32" t="n">
@@ -7670,7 +7682,7 @@
     <row r="367">
       <c r="B367" s="31" t="inlineStr">
         <is>
-          <t>Шампунь увлажняющий д/волос 1000 мл 4910/10582</t>
+          <t>Шампунь увлажняющий для волос 1000мл 4910/10582</t>
         </is>
       </c>
       <c r="C367" s="36" t="n">
@@ -7692,10 +7704,10 @@
           <t>MATRIX</t>
         </is>
       </c>
-      <c r="C368" s="16" t="n"/>
+      <c r="C368" s="43" t="n"/>
       <c r="D368" s="24" t="n"/>
-      <c r="E368" s="25" t="n"/>
-      <c r="F368" s="26" t="n"/>
+      <c r="E368" s="24" t="n"/>
+      <c r="F368" s="44" t="n"/>
     </row>
     <row r="369" ht="14.25" customHeight="1">
       <c r="B369" s="12" t="inlineStr">
@@ -7703,15 +7715,15 @@
           <t>Total Results New</t>
         </is>
       </c>
-      <c r="C369" s="17" t="n"/>
+      <c r="C369" s="45" t="n"/>
       <c r="D369" s="24" t="n"/>
-      <c r="E369" s="25" t="n"/>
-      <c r="F369" s="37" t="n"/>
+      <c r="E369" s="24" t="n"/>
+      <c r="F369" s="44" t="n"/>
     </row>
     <row r="370">
       <c r="B370" s="31" t="inlineStr">
         <is>
-          <t>Дозатор 1000 мл. 12218</t>
+          <t>Дозатор 1000мл 12218</t>
         </is>
       </c>
       <c r="C370" s="32" t="n">
@@ -7730,7 +7742,7 @@
     <row r="371" ht="22.5" customHeight="1">
       <c r="B371" s="31" t="inlineStr">
         <is>
-          <t>Кондиционер Brass Off 1000 ml. (нейтрализует желтые подтона на волосах 5-8 уровней) 2235800</t>
+          <t>Кондиционер Brass Off 1000мл (нейтрализует желтые подтона на волосах 5-8 уровней) 2235800</t>
         </is>
       </c>
       <c r="C371" s="36" t="n">
@@ -7749,7 +7761,7 @@
     <row r="372" ht="22.5" customHeight="1">
       <c r="B372" s="7" t="inlineStr">
         <is>
-          <t>Кондиционер Brass Off 300 ml. (нейтрализует желтые подтона на волосах 5-8 уровней) 2235400</t>
+          <t>Кондиционер Brass Off 300мл (нейтрализует желтые подтона на волосах 5-8 уровней) 2235400</t>
         </is>
       </c>
       <c r="C372" s="8" t="n">
@@ -7768,7 +7780,7 @@
     <row r="373" ht="22.5" customHeight="1">
       <c r="B373" s="7" t="inlineStr">
         <is>
-          <t>Кондиционер Color Obsessed So Silver 1000 ml. (нейтрализует желтые подтона на волосах 8-11 уровней) 307010/2990300</t>
+          <t>Кондиционер Color Obsessed So Silver 1000мл (нейтрализует желтые подтона на волосах 8-11 уровней) 307010/2990300</t>
         </is>
       </c>
       <c r="C373" s="10" t="n">
@@ -7787,7 +7799,7 @@
     <row r="374">
       <c r="B374" s="7" t="inlineStr">
         <is>
-          <t>Кондиционер Color Obsessed для окрашенных волос 1000 ml. 302703</t>
+          <t>Кондиционер Color Obsessed для окрашенных волос 1000мл 302703</t>
         </is>
       </c>
       <c r="C374" s="10" t="n">
@@ -7806,7 +7818,7 @@
     <row r="375" ht="22.5" customHeight="1">
       <c r="B375" s="7" t="inlineStr">
         <is>
-          <t>Кондиционер Food For Soft увлажнение с авокадо и гиалур. 1000 ml. 305815/4013700</t>
+          <t>Кондиционер Food For Soft увлажнение с авокадо и гиалуроновой кислотой 1000мл 305815/4013700</t>
         </is>
       </c>
       <c r="C375" s="10" t="n">
@@ -7825,7 +7837,7 @@
     <row r="376">
       <c r="B376" s="7" t="inlineStr">
         <is>
-          <t>Кондиционер High Amplify для объема 1000 ml. 304144/1574600</t>
+          <t>Кондиционер High Amplify для объёма 1000мл 304144/1574600</t>
         </is>
       </c>
       <c r="C376" s="10" t="n">
@@ -7844,7 +7856,7 @@
     <row r="377">
       <c r="B377" s="7" t="inlineStr">
         <is>
-          <t>Кондиционер High Amplify для объема 300 ml. 311656</t>
+          <t>Кондиционер High Amplify для объёма 300мл 311656</t>
         </is>
       </c>
       <c r="C377" s="8" t="n">
@@ -7863,7 +7875,7 @@
     <row r="378" ht="22.5" customHeight="1">
       <c r="B378" s="7" t="inlineStr">
         <is>
-          <t>Кондиционер Instacure Бонд Anti-Breakage против ломкости 300 ml. 308093/3824300</t>
+          <t>Кондиционер Instacure Бонд Anti-Breakage против ломкости 300мл 308093/3824300</t>
         </is>
       </c>
       <c r="C378" s="10" t="n">
@@ -7882,7 +7894,7 @@
     <row r="379" ht="22.5" customHeight="1">
       <c r="B379" s="7" t="inlineStr">
         <is>
-          <t>Шамп. Color Obsessed So Silver 300 ml. (нейтрализует желтые подтона на волосах 8-11 уровней) 312459/1577700</t>
+          <t>Шампунь Color Obsessed So Silver 300мл (нейтрализует желтые подтона на волосах 8-11 уровней) 312459/1577700</t>
         </is>
       </c>
       <c r="C379" s="8" t="n">
@@ -7901,7 +7913,7 @@
     <row r="380">
       <c r="B380" s="7" t="inlineStr">
         <is>
-          <t>Шамп. Food For Soft увлажнение с авокадо и гиалур. 300 ml. 305811</t>
+          <t>Шампунь Food For Soft увлажнение с авокадо и гиалуроновой кислотой 300мл 305811</t>
         </is>
       </c>
       <c r="C380" s="8" t="n">
@@ -7920,7 +7932,7 @@
     <row r="381" ht="22.5" customHeight="1">
       <c r="B381" s="7" t="inlineStr">
         <is>
-          <t>Шамп. Instacure Anti-Breakage против ломкости 300 ml. 308092/3824800</t>
+          <t>Шампунь Instacure Anti-Breakage против ломкости 300мл 308092/3824800</t>
         </is>
       </c>
       <c r="C381" s="8" t="n">
@@ -7939,7 +7951,7 @@
     <row r="382" ht="22.5" customHeight="1">
       <c r="B382" s="7" t="inlineStr">
         <is>
-          <t>Шамп. Instacure Бонд Anti-Breakage против ломкости 1000 ml. 308096</t>
+          <t>Шампунь Instacure Бонд Anti-Breakage против ломкости 1000мл 308096</t>
         </is>
       </c>
       <c r="C382" s="10" t="n">
@@ -7961,15 +7973,15 @@
           <t>MATRIX</t>
         </is>
       </c>
-      <c r="C383" s="17" t="n"/>
+      <c r="C383" s="45" t="n"/>
       <c r="D383" s="24" t="n"/>
-      <c r="E383" s="25" t="n"/>
-      <c r="F383" s="37" t="n"/>
+      <c r="E383" s="24" t="n"/>
+      <c r="F383" s="44" t="n"/>
     </row>
     <row r="384">
       <c r="B384" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 10G 90 мл. 010G</t>
+          <t>Color Sync 10G 90мл 010G</t>
         </is>
       </c>
       <c r="C384" s="8" t="n">
@@ -7988,7 +8000,7 @@
     <row r="385">
       <c r="B385" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 10N 90 мл. 010N</t>
+          <t>Color Sync 10N 90мл 010N</t>
         </is>
       </c>
       <c r="C385" s="8" t="n">
@@ -8007,7 +8019,7 @@
     <row r="386">
       <c r="B386" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 10NV 90 мл. NEW 010NV</t>
+          <t>Color Sync 10NV 90мл NEW 010NV</t>
         </is>
       </c>
       <c r="C386" s="8" t="n">
@@ -8026,7 +8038,7 @@
     <row r="387">
       <c r="B387" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 10P оч-оч. св. блонд. жемчуж. 90 мл. 010P</t>
+          <t>Color Sync 10P очень светлый блонд жемчужный 90мл 010P</t>
         </is>
       </c>
       <c r="C387" s="8" t="n">
@@ -8045,7 +8057,7 @@
     <row r="388">
       <c r="B388" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 11A 90 мл. 011A</t>
+          <t>Color Sync 11A 90мл 011A</t>
         </is>
       </c>
       <c r="C388" s="8" t="n">
@@ -8064,7 +8076,7 @@
     <row r="389">
       <c r="B389" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 11P 90 мл. 011P</t>
+          <t>Color Sync 11P 90мл 011P</t>
         </is>
       </c>
       <c r="C389" s="8" t="n">
@@ -8083,7 +8095,7 @@
     <row r="390">
       <c r="B390" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 1A 90 мл. 01A</t>
+          <t>Color Sync 1A 90мл 01A</t>
         </is>
       </c>
       <c r="C390" s="8" t="n">
@@ -8102,7 +8114,7 @@
     <row r="391">
       <c r="B391" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 3N 90 мл. 03N</t>
+          <t>Color Sync 3N 90мл 03N</t>
         </is>
       </c>
       <c r="C391" s="8" t="n">
@@ -8121,7 +8133,7 @@
     <row r="392">
       <c r="B392" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 3NN 90ml      NEW 03NN</t>
+          <t>Color Sync 3NN 90мл NEW 03NN</t>
         </is>
       </c>
       <c r="C392" s="8" t="n">
@@ -8140,7 +8152,7 @@
     <row r="393">
       <c r="B393" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 4A 90 мл. 04A</t>
+          <t>Color Sync 4A 90мл 04A</t>
         </is>
       </c>
       <c r="C393" s="8" t="n">
@@ -8159,7 +8171,7 @@
     <row r="394">
       <c r="B394" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 4BR шатен коричневый красный 90 мл NEW 04BR</t>
+          <t>Color Sync 4BR шатен коричневый красный 90мл NEW 04BR</t>
         </is>
       </c>
       <c r="C394" s="8" t="n">
@@ -8197,7 +8209,7 @@
     <row r="396">
       <c r="B396" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 4T шатен титановый 90 мл. NEW 04T</t>
+          <t>Color Sync 4T шатен титановый 90мл NEW 04T</t>
         </is>
       </c>
       <c r="C396" s="8" t="n">
@@ -8216,7 +8228,7 @@
     <row r="397">
       <c r="B397" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 5M 90 мл. 05M</t>
+          <t>Color Sync 5M 90мл 05M</t>
         </is>
       </c>
       <c r="C397" s="8" t="n">
@@ -8235,7 +8247,7 @@
     <row r="398">
       <c r="B398" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 5N св. шатен 90 мл. 05N</t>
+          <t>Color Sync 5N светлый шатен 90мл 05N</t>
         </is>
       </c>
       <c r="C398" s="8" t="n">
@@ -8254,7 +8266,7 @@
     <row r="399">
       <c r="B399" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 5NN св. шатен глубокий 90 мл. NEW 05NN</t>
+          <t>Color Sync 5NN светлый шатен глубокий 90мл NEW 05NN</t>
         </is>
       </c>
       <c r="C399" s="8" t="n">
@@ -8273,7 +8285,7 @@
     <row r="400">
       <c r="B400" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 5WN 90 мл. 05WN</t>
+          <t>Color Sync 5WN 90мл 05WN</t>
         </is>
       </c>
       <c r="C400" s="8" t="n">
@@ -8292,7 +8304,7 @@
     <row r="401">
       <c r="B401" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6A 90 мл. 06A</t>
+          <t>Color Sync 6A 90мл 06A</t>
         </is>
       </c>
       <c r="C401" s="8" t="n">
@@ -8311,7 +8323,7 @@
     <row r="402">
       <c r="B402" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6BC 90 мл. 06BC</t>
+          <t>Color Sync 6BC 90мл 06BC</t>
         </is>
       </c>
       <c r="C402" s="8" t="n">
@@ -8330,7 +8342,7 @@
     <row r="403">
       <c r="B403" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6BR 90 мл. 06BR</t>
+          <t>Color Sync 6BR 90мл 06BR</t>
         </is>
       </c>
       <c r="C403" s="8" t="n">
@@ -8349,7 +8361,7 @@
     <row r="404">
       <c r="B404" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6CG 90 мл.   NEW 06CG</t>
+          <t>Color Sync 6CG 90мл NEW 06CG</t>
         </is>
       </c>
       <c r="C404" s="8" t="n">
@@ -8368,7 +8380,7 @@
     <row r="405">
       <c r="B405" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6M 90 мл. 06M</t>
+          <t>Color Sync 6M 90мл 06M</t>
         </is>
       </c>
       <c r="C405" s="8" t="n">
@@ -8387,7 +8399,7 @@
     <row r="406">
       <c r="B406" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6N блонд. темный 90 мл. 06N</t>
+          <t>Color Sync 6N блонд темный 90мл 06N</t>
         </is>
       </c>
       <c r="C406" s="8" t="n">
@@ -8406,7 +8418,7 @@
     <row r="407">
       <c r="B407" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6P 90 мл.   NEW 06P</t>
+          <t>Color Sync 6P 90мл NEW 06P</t>
         </is>
       </c>
       <c r="C407" s="8" t="n">
@@ -8425,7 +8437,7 @@
     <row r="408">
       <c r="B408" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6RB 90 мл.    NEW 06RB</t>
+          <t>Color Sync 6RB 90мл NEW 06RB</t>
         </is>
       </c>
       <c r="C408" s="8" t="n">
@@ -8444,7 +8456,7 @@
     <row r="409">
       <c r="B409" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6RC+ 90 мл.    NEW 06RC+</t>
+          <t>Color Sync 6RC+ 90мл NEW 06RC+</t>
         </is>
       </c>
       <c r="C409" s="8" t="n">
@@ -8463,7 +8475,7 @@
     <row r="410" ht="22.5" customHeight="1">
       <c r="B410" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6RV+ темный блонд. красно-перлпмутр. 90 мл    NEW 06RV+</t>
+          <t>Color Sync 6RV+ темный блонд красно-перлапмутровый 90мл NEW 06RV+</t>
         </is>
       </c>
       <c r="C410" s="8" t="n">
@@ -8482,7 +8494,7 @@
     <row r="411">
       <c r="B411" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6T темный блонд титановый 90 мл.   NEW 06T</t>
+          <t>Color Sync 6T темный блонд титановый 90мл NEW 06T</t>
         </is>
       </c>
       <c r="C411" s="8" t="n">
@@ -8501,7 +8513,7 @@
     <row r="412">
       <c r="B412" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 6WN 90 мл. 06WN</t>
+          <t>Color Sync 6WN 90мл 06WN</t>
         </is>
       </c>
       <c r="C412" s="8" t="n">
@@ -8520,7 +8532,7 @@
     <row r="413" ht="22.5" customHeight="1">
       <c r="B413" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 7NA Pre-Bonded блондин натуральный пепельный 90 мл 07NA</t>
+          <t>Color Sync 7NA Pre-Bonded блондин натуральный пепельный 90мл 07NA</t>
         </is>
       </c>
       <c r="C413" s="8" t="n">
@@ -8539,7 +8551,7 @@
     <row r="414">
       <c r="B414" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 7RR+ глубокий красный 90 мл.  NEW 07RR+</t>
+          <t>Color Sync 7RR+ глубокий красный 90мл NEW 07RR+</t>
         </is>
       </c>
       <c r="C414" s="8" t="n">
@@ -8558,7 +8570,7 @@
     <row r="415">
       <c r="B415" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 8A 90 мл. 08A</t>
+          <t>Color Sync 8A 90мл 08A</t>
         </is>
       </c>
       <c r="C415" s="8" t="n">
@@ -8577,7 +8589,7 @@
     <row r="416">
       <c r="B416" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 8BC 90 мл. 08BC</t>
+          <t>Color Sync 8BC 90мл 08BC</t>
         </is>
       </c>
       <c r="C416" s="8" t="n">
@@ -8596,7 +8608,7 @@
     <row r="417">
       <c r="B417" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 8G 90 мл. 08G</t>
+          <t>Color Sync 8G 90мл 08G</t>
         </is>
       </c>
       <c r="C417" s="8" t="n">
@@ -8615,7 +8627,7 @@
     <row r="418">
       <c r="B418" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 8NN блондин светлый глубокий 90 мл.   NEW 08NN</t>
+          <t>Color Sync 8NN блондин светлый глубокий 90мл NEW 08NN</t>
         </is>
       </c>
       <c r="C418" s="8" t="n">
@@ -8653,7 +8665,7 @@
     <row r="420">
       <c r="B420" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 8WN 90 мл. 08WN</t>
+          <t>Color Sync 8WN 90мл 08WN</t>
         </is>
       </c>
       <c r="C420" s="8" t="n">
@@ -8710,7 +8722,7 @@
     <row r="423" ht="22.5" customHeight="1">
       <c r="B423" s="7" t="inlineStr">
         <is>
-          <t>Color Sync 9NA Pre-Bonded очень светлый блондин натуральный пепельный 90 мл 09NA</t>
+          <t>Color Sync 9NA Pre-Bonded очень светлый блондин натуральный пепельный 90мл 09NA</t>
         </is>
       </c>
       <c r="C423" s="8" t="n">
@@ -8729,7 +8741,7 @@
     <row r="424">
       <c r="B424" s="7" t="inlineStr">
         <is>
-          <t>Color Sync CLEAR ПРОЗРАЧНЫЙ оттенок 90 мл. CLEAR/99989414493</t>
+          <t>Color Sync CLEAR ПРОЗРАЧНЫЙ оттенок 90мл CLEAR/99989414493</t>
         </is>
       </c>
       <c r="C424" s="8" t="n">
@@ -8748,7 +8760,7 @@
     <row r="425">
       <c r="B425" s="7" t="inlineStr">
         <is>
-          <t>Color Sync HD-RR глубокий красный 90 мл. NEW HD-RR</t>
+          <t>Color Sync HD-RR глубокий красный 90мл NEW HD-RR</t>
         </is>
       </c>
       <c r="C425" s="8" t="n">
@@ -8767,7 +8779,7 @@
     <row r="426">
       <c r="B426" s="7" t="inlineStr">
         <is>
-          <t>Color Sync HD-RV красно-перламутровый 90 мл. NEW HD-RV</t>
+          <t>Color Sync HD-RV красно-перламутровый 90мл NEW HD-RV</t>
         </is>
       </c>
       <c r="C426" s="8" t="n">
@@ -8843,7 +8855,7 @@
     <row r="430">
       <c r="B430" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 10AG 90 мл 0-10AG</t>
+          <t>Color Sync Тонер с Кислым Ph 10AG 90мл 0-10AG</t>
         </is>
       </c>
       <c r="C430" s="8" t="n">
@@ -8862,7 +8874,7 @@
     <row r="431">
       <c r="B431" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 10GB 90 мл 0-10GB</t>
+          <t>Color Sync Тонер с Кислым Ph 10GB 90мл 0-10GB</t>
         </is>
       </c>
       <c r="C431" s="8" t="n">
@@ -8881,7 +8893,7 @@
     <row r="432">
       <c r="B432" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 10N 90 мл 0-10N</t>
+          <t>Color Sync Тонер с Кислым Ph 10N 90мл 0-10N</t>
         </is>
       </c>
       <c r="C432" s="8" t="n">
@@ -8900,7 +8912,7 @@
     <row r="433">
       <c r="B433" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 10P 90 мл 0-10P</t>
+          <t>Color Sync Тонер с Кислым Ph 10P 90мл 0-10P</t>
         </is>
       </c>
       <c r="C433" s="8" t="n">
@@ -8919,7 +8931,7 @@
     <row r="434">
       <c r="B434" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 10PA 90 мл 0-10PA</t>
+          <t>Color Sync Тонер с Кислым Ph 10PA 90мл 0-10PA</t>
         </is>
       </c>
       <c r="C434" s="8" t="n">
@@ -8938,7 +8950,7 @@
     <row r="435">
       <c r="B435" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 10PR 90 мл 0-10PR</t>
+          <t>Color Sync Тонер с Кислым Ph 10PR 90мл 0-10PR</t>
         </is>
       </c>
       <c r="C435" s="8" t="n">
@@ -8957,7 +8969,7 @@
     <row r="436">
       <c r="B436" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 10T 90 мл 0-10T</t>
+          <t>Color Sync Тонер с Кислым Ph 10T 90мл 0-10T</t>
         </is>
       </c>
       <c r="C436" s="8" t="n">
@@ -8976,7 +8988,7 @@
     <row r="437">
       <c r="B437" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 11N 90 мл 0-11N</t>
+          <t>Color Sync Тонер с Кислым Ph 11N 90мл 0-11N</t>
         </is>
       </c>
       <c r="C437" s="8" t="n">
@@ -8995,7 +9007,7 @@
     <row r="438">
       <c r="B438" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 11NA 90 мл 0-11NA</t>
+          <t>Color Sync Тонер с Кислым Ph 11NA 90мл 0-11NA</t>
         </is>
       </c>
       <c r="C438" s="8" t="n">
@@ -9014,7 +9026,7 @@
     <row r="439">
       <c r="B439" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 11NV 90 мл 0-11NV</t>
+          <t>Color Sync Тонер с Кислым Ph 11NV 90мл 0-11NV</t>
         </is>
       </c>
       <c r="C439" s="8" t="n">
@@ -9033,7 +9045,7 @@
     <row r="440">
       <c r="B440" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 11PA 90 мл 0-11PA</t>
+          <t>Color Sync Тонер с Кислым Ph 11PA 90мл 0-11PA</t>
         </is>
       </c>
       <c r="C440" s="8" t="n">
@@ -9052,7 +9064,7 @@
     <row r="441">
       <c r="B441" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 7GM 90 мл 0-7GM</t>
+          <t>Color Sync Тонер с Кислым Ph 7GM 90мл 0-7GM</t>
         </is>
       </c>
       <c r="C441" s="8" t="n">
@@ -9071,7 +9083,7 @@
     <row r="442">
       <c r="B442" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 8C 90 мл 0-8C</t>
+          <t>Color Sync Тонер с Кислым Ph 8C 90мл 0-8C</t>
         </is>
       </c>
       <c r="C442" s="8" t="n">
@@ -9090,7 +9102,7 @@
     <row r="443">
       <c r="B443" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 8CR 90 мл 0-8CR</t>
+          <t>Color Sync Тонер с Кислым Ph 8CR 90мл 0-8CR</t>
         </is>
       </c>
       <c r="C443" s="8" t="n">
@@ -9109,7 +9121,7 @@
     <row r="444">
       <c r="B444" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 8GB 90 мл 0-8GB</t>
+          <t>Color Sync Тонер с Кислым Ph 8GB 90мл 0-8GB</t>
         </is>
       </c>
       <c r="C444" s="8" t="n">
@@ -9128,7 +9140,7 @@
     <row r="445">
       <c r="B445" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 8P 90 мл 0-8P</t>
+          <t>Color Sync Тонер с Кислым Ph 8P 90мл 0-8P</t>
         </is>
       </c>
       <c r="C445" s="8" t="n">
@@ -9147,7 +9159,7 @@
     <row r="446">
       <c r="B446" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 8T 90 мл 0-8T</t>
+          <t>Color Sync Тонер с Кислым Ph 8T 90мл 0-8T</t>
         </is>
       </c>
       <c r="C446" s="8" t="n">
@@ -9166,7 +9178,7 @@
     <row r="447">
       <c r="B447" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 8VG 90 мл 0-8VG</t>
+          <t>Color Sync Тонер с Кислым Ph 8VG 90мл 0-8VG</t>
         </is>
       </c>
       <c r="C447" s="8" t="n">
@@ -9185,7 +9197,7 @@
     <row r="448">
       <c r="B448" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 8VR 90 мл 0-8VR</t>
+          <t>Color Sync Тонер с Кислым Ph 8VR 90мл 0-8VR</t>
         </is>
       </c>
       <c r="C448" s="8" t="n">
@@ -9204,7 +9216,7 @@
     <row r="449">
       <c r="B449" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 9AA 90 мл 0-9AA</t>
+          <t>Color Sync Тонер с Кислым Ph 9AA 90мл 0-9AA</t>
         </is>
       </c>
       <c r="C449" s="8" t="n">
@@ -9223,7 +9235,7 @@
     <row r="450">
       <c r="B450" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 9G 90 мл 0-9G</t>
+          <t>Color Sync Тонер с Кислым Ph 9G 90мл 0-9G</t>
         </is>
       </c>
       <c r="C450" s="8" t="n">
@@ -9242,7 +9254,7 @@
     <row r="451">
       <c r="B451" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 9GV 90 мл 0-9GV</t>
+          <t>Color Sync Тонер с Кислым Ph 9GV 90мл 0-9GV</t>
         </is>
       </c>
       <c r="C451" s="8" t="n">
@@ -9261,7 +9273,7 @@
     <row r="452">
       <c r="B452" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 9NCV 90 мл 0-9NCV</t>
+          <t>Color Sync Тонер с Кислым Ph 9NCV 90мл 0-9NCV</t>
         </is>
       </c>
       <c r="C452" s="8" t="n">
@@ -9280,7 +9292,7 @@
     <row r="453">
       <c r="B453" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 9NW 90 мл 0-9NW</t>
+          <t>Color Sync Тонер с Кислым Ph 9NW 90мл 0-9NW</t>
         </is>
       </c>
       <c r="C453" s="8" t="n">
@@ -9318,7 +9330,7 @@
     <row r="455">
       <c r="B455" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 9V 90 мл 0-9V</t>
+          <t>Color Sync Тонер с Кислым Ph 9V 90мл 0-9V</t>
         </is>
       </c>
       <c r="C455" s="8" t="n">
@@ -9337,7 +9349,7 @@
     <row r="456">
       <c r="B456" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph 9W 90 мл 0-9W</t>
+          <t>Color Sync Тонер с Кислым Ph 9W 90мл 0-9W</t>
         </is>
       </c>
       <c r="C456" s="8" t="n">
@@ -9356,7 +9368,7 @@
     <row r="457">
       <c r="B457" s="7" t="inlineStr">
         <is>
-          <t>Color Sync Тонер с Кислым Ph CLEAR 90 мл 0-CLEAR</t>
+          <t>Color Sync Тонер с Кислым Ph CLEAR 90мл 0-CLEAR</t>
         </is>
       </c>
       <c r="C457" s="8" t="n">
@@ -9546,7 +9558,7 @@
     <row r="467">
       <c r="B467" s="7" t="inlineStr">
         <is>
-          <t>Socolor 4AA 90 мл. 4AA</t>
+          <t>Socolor 4AA 90мл 4AA</t>
         </is>
       </c>
       <c r="C467" s="8" t="n">
@@ -10629,7 +10641,7 @@
     <row r="524">
       <c r="B524" s="7" t="inlineStr">
         <is>
-          <t>Socolor CLEAR.90 мл s-clear/3709400</t>
+          <t>Socolor CLEAR 90мл s-clear/3709400</t>
         </is>
       </c>
       <c r="C524" s="8" t="n">
@@ -10686,7 +10698,7 @@
     <row r="527">
       <c r="B527" s="7" t="inlineStr">
         <is>
-          <t>Socolor UL-NV+ натур. перламутр.+ UL-NV+</t>
+          <t>Socolor UL-NV+ натуральный перламутровый + UL-NV+</t>
         </is>
       </c>
       <c r="C527" s="8" t="n">
@@ -10762,7 +10774,7 @@
     <row r="531">
       <c r="B531" s="31" t="inlineStr">
         <is>
-          <t>Оксид Socolor 12% 1000 мл. 99989418180</t>
+          <t>Оксид Socolor 12% 1000мл 99989418180</t>
         </is>
       </c>
       <c r="C531" s="36" t="n">
@@ -10781,7 +10793,7 @@
     <row r="532">
       <c r="B532" s="31" t="inlineStr">
         <is>
-          <t>Оксид Socolor 9% 1000 мл. 308147</t>
+          <t>Оксид Socolor 9% 1000мл 308147</t>
         </is>
       </c>
       <c r="C532" s="36" t="n">
@@ -10800,7 +10812,7 @@
     <row r="533">
       <c r="B533" s="7" t="inlineStr">
         <is>
-          <t>Оксид Socolor/ Color Sync 3% 60 мл. 290876</t>
+          <t>Оксид Socolor/ Color Sync 3% 60мл 290876</t>
         </is>
       </c>
       <c r="C533" s="8" t="n">
@@ -10819,7 +10831,7 @@
     <row r="534" ht="22.5" customHeight="1">
       <c r="B534" s="7" t="inlineStr">
         <is>
-          <t>Супра, фиолетовый пакет Light Master с Бондером 8 уровней 500 г. 3779500/3453600</t>
+          <t>Супра, фиолетовый пакет Light Master с Бондером 8 уровней 500г 3779500/3453600</t>
         </is>
       </c>
       <c r="C534" s="10" t="n">
@@ -10841,10 +10853,10 @@
           <t>OLLIN</t>
         </is>
       </c>
-      <c r="C535" s="16" t="n"/>
+      <c r="C535" s="43" t="n"/>
       <c r="D535" s="24" t="n"/>
-      <c r="E535" s="25" t="n"/>
-      <c r="F535" s="26" t="n"/>
+      <c r="E535" s="24" t="n"/>
+      <c r="F535" s="44" t="n"/>
     </row>
     <row r="536">
       <c r="B536" s="7" t="inlineStr">
@@ -10982,7 +10994,7 @@
     <row r="543">
       <c r="B543" s="7" t="inlineStr">
         <is>
-          <t>Color 10/1, 60 мл. св. блондин пепел. 10-1</t>
+          <t>Color 10/1 60мл светлый блондин пепельный 10-1</t>
         </is>
       </c>
       <c r="C543" s="8" t="n">
@@ -11723,7 +11735,7 @@
     <row r="582">
       <c r="B582" s="7" t="inlineStr">
         <is>
-          <t>Color 7/4, 60 мл. русый медный 7-4</t>
+          <t>Color 7/4 60мл русый медный 7-4</t>
         </is>
       </c>
       <c r="C582" s="8" t="n">
@@ -11742,7 +11754,7 @@
     <row r="583">
       <c r="B583" s="7" t="inlineStr">
         <is>
-          <t>Color 7/43, 60 мл. русый медно-золотистый 7-43</t>
+          <t>Color 7/43 60мл русый медно-золотистый 7-43</t>
         </is>
       </c>
       <c r="C583" s="8" t="n">
@@ -12141,7 +12153,7 @@
     <row r="604" ht="22.5" customHeight="1">
       <c r="B604" s="31" t="inlineStr">
         <is>
-          <t>Fashion Color Анти-желтый 60мл Перманентная крем-краска для волос 395645</t>
+          <t>Fashion Color Анти-желтый 60мл 395645</t>
         </is>
       </c>
       <c r="C604" s="32" t="n">
@@ -12236,7 +12248,7 @@
     <row r="609">
       <c r="B609" s="31" t="inlineStr">
         <is>
-          <t>Performanse 0-25 60ml 0-025</t>
+          <t>Performanse 0-25 60мл 0-025</t>
         </is>
       </c>
       <c r="C609" s="32" t="n">
@@ -12255,7 +12267,7 @@
     <row r="610">
       <c r="B610" s="31" t="inlineStr">
         <is>
-          <t>Performanse 0-33 60ml 0-033</t>
+          <t>Performanse 0-33 60мл 0-033</t>
         </is>
       </c>
       <c r="C610" s="32" t="n">
@@ -12274,7 +12286,7 @@
     <row r="611">
       <c r="B611" s="31" t="inlineStr">
         <is>
-          <t>Performanse 0-66 60ml 0-066</t>
+          <t>Performanse 0-66 60мл 0-066</t>
         </is>
       </c>
       <c r="C611" s="32" t="n">
@@ -12293,7 +12305,7 @@
     <row r="612">
       <c r="B612" s="31" t="inlineStr">
         <is>
-          <t>Performanse 0-88 60ml фиолетовый 0-088</t>
+          <t>Performanse 0-88 60мл фиолетовый 0-088</t>
         </is>
       </c>
       <c r="C612" s="32" t="n">
@@ -12312,7 +12324,7 @@
     <row r="613">
       <c r="B613" s="31" t="inlineStr">
         <is>
-          <t>Performanse 1-0  60ml 0-1</t>
+          <t>Performanse 1-0 60мл 0-1</t>
         </is>
       </c>
       <c r="C613" s="32" t="n">
@@ -12331,7 +12343,7 @@
     <row r="614">
       <c r="B614" s="31" t="inlineStr">
         <is>
-          <t>Performanse 10-31  60ml 0-1031</t>
+          <t>Performanse 10-31 60мл 0-1031</t>
         </is>
       </c>
       <c r="C614" s="32" t="n">
@@ -12350,7 +12362,7 @@
     <row r="615">
       <c r="B615" s="7" t="inlineStr">
         <is>
-          <t>Performanse 10-43  60ml 0-1043</t>
+          <t>Performanse 10-43 60мл 0-1043</t>
         </is>
       </c>
       <c r="C615" s="8" t="n">
@@ -12369,7 +12381,7 @@
     <row r="616">
       <c r="B616" s="31" t="inlineStr">
         <is>
-          <t>Performanse 10-72  60ml 0-1072</t>
+          <t>Performanse 10-72 60мл 0-1072</t>
         </is>
       </c>
       <c r="C616" s="32" t="n">
@@ -12388,7 +12400,7 @@
     <row r="617">
       <c r="B617" s="31" t="inlineStr">
         <is>
-          <t>Performanse 10-73  60ml 0-1073</t>
+          <t>Performanse 10-73 60мл 0-1073</t>
         </is>
       </c>
       <c r="C617" s="32" t="n">
@@ -12407,7 +12419,7 @@
     <row r="618">
       <c r="B618" s="31" t="inlineStr">
         <is>
-          <t>Performanse 11-1 60ml 0-111</t>
+          <t>Performanse 11-1 60мл 0-111</t>
         </is>
       </c>
       <c r="C618" s="32" t="n">
@@ -12426,7 +12438,7 @@
     <row r="619">
       <c r="B619" s="7" t="inlineStr">
         <is>
-          <t>Performanse 11-12 60ml 0-1112</t>
+          <t>Performanse 11-12 60мл 0-1112</t>
         </is>
       </c>
       <c r="C619" s="8" t="n">
@@ -12445,7 +12457,7 @@
     <row r="620">
       <c r="B620" s="31" t="inlineStr">
         <is>
-          <t>Performanse 11-3 60ml 0-113</t>
+          <t>Performanse 11-3 60мл 0-113</t>
         </is>
       </c>
       <c r="C620" s="32" t="n">
@@ -12464,7 +12476,7 @@
     <row r="621">
       <c r="B621" s="7" t="inlineStr">
         <is>
-          <t>Performanse 11-31 60ml 0-1131</t>
+          <t>Performanse 11-31 60мл 0-1131</t>
         </is>
       </c>
       <c r="C621" s="8" t="n">
@@ -12483,7 +12495,7 @@
     <row r="622">
       <c r="B622" s="31" t="inlineStr">
         <is>
-          <t>Performanse 11-7 60ml 0-117</t>
+          <t>Performanse 11-7 60мл 0-117</t>
         </is>
       </c>
       <c r="C622" s="32" t="n">
@@ -12502,7 +12514,7 @@
     <row r="623">
       <c r="B623" s="31" t="inlineStr">
         <is>
-          <t>Performanse 2-0  60ml 0-20</t>
+          <t>Performanse 2-0 60мл 0-20</t>
         </is>
       </c>
       <c r="C623" s="32" t="n">
@@ -12521,7 +12533,7 @@
     <row r="624">
       <c r="B624" s="31" t="inlineStr">
         <is>
-          <t>Performanse 2-22  60ml 0-222</t>
+          <t>Performanse 2-22 60мл 0-222</t>
         </is>
       </c>
       <c r="C624" s="32" t="n">
@@ -12540,7 +12552,7 @@
     <row r="625">
       <c r="B625" s="31" t="inlineStr">
         <is>
-          <t>Performanse 4-3  60ml 0-43</t>
+          <t>Performanse 4-3 60мл 0-43</t>
         </is>
       </c>
       <c r="C625" s="32" t="n">
@@ -12559,7 +12571,7 @@
     <row r="626">
       <c r="B626" s="7" t="inlineStr">
         <is>
-          <t>Performanse 4-5  60ml 0-45</t>
+          <t>Performanse 4-5 60мл 0-45</t>
         </is>
       </c>
       <c r="C626" s="8" t="n">
@@ -12578,7 +12590,7 @@
     <row r="627">
       <c r="B627" s="31" t="inlineStr">
         <is>
-          <t>Performanse 5-09 60ml 0-509</t>
+          <t>Performanse 5-09 60мл 0-509</t>
         </is>
       </c>
       <c r="C627" s="32" t="n">
@@ -12597,7 +12609,7 @@
     <row r="628">
       <c r="B628" s="31" t="inlineStr">
         <is>
-          <t>Performanse 5-1 60ml 0-51</t>
+          <t>Performanse 5-1 60мл 0-51</t>
         </is>
       </c>
       <c r="C628" s="32" t="n">
@@ -12616,7 +12628,7 @@
     <row r="629">
       <c r="B629" s="7" t="inlineStr">
         <is>
-          <t>Performanse 5-22 60ml 0-522</t>
+          <t>Performanse 5-22 60мл 0-522</t>
         </is>
       </c>
       <c r="C629" s="8" t="n">
@@ -12635,7 +12647,7 @@
     <row r="630">
       <c r="B630" s="31" t="inlineStr">
         <is>
-          <t>Performanse 5-3 60ml 0-53</t>
+          <t>Performanse 5-3 60мл 0-53</t>
         </is>
       </c>
       <c r="C630" s="32" t="n">
@@ -12654,7 +12666,7 @@
     <row r="631">
       <c r="B631" s="31" t="inlineStr">
         <is>
-          <t>Performanse 5-4 60ml 0-54</t>
+          <t>Performanse 5-4 60мл 0-54</t>
         </is>
       </c>
       <c r="C631" s="32" t="n">
@@ -12673,7 +12685,7 @@
     <row r="632">
       <c r="B632" s="31" t="inlineStr">
         <is>
-          <t>Performanse 5-5 60ml 0-55</t>
+          <t>Performanse 5-5 60мл 0-55</t>
         </is>
       </c>
       <c r="C632" s="32" t="n">
@@ -12692,7 +12704,7 @@
     <row r="633">
       <c r="B633" s="31" t="inlineStr">
         <is>
-          <t>Performanse 6-09 60ml 0-609</t>
+          <t>Performanse 6-09 60мл 0-609</t>
         </is>
       </c>
       <c r="C633" s="32" t="n">
@@ -12711,7 +12723,7 @@
     <row r="634">
       <c r="B634" s="31" t="inlineStr">
         <is>
-          <t>Performanse 6-22 60ml 0-622</t>
+          <t>Performanse 6-22 60мл 0-622</t>
         </is>
       </c>
       <c r="C634" s="32" t="n">
@@ -12730,7 +12742,7 @@
     <row r="635">
       <c r="B635" s="31" t="inlineStr">
         <is>
-          <t>Performanse 6-3  60ml 0-63</t>
+          <t>Performanse 6-3 60мл 0-63</t>
         </is>
       </c>
       <c r="C635" s="32" t="n">
@@ -12749,7 +12761,7 @@
     <row r="636">
       <c r="B636" s="31" t="inlineStr">
         <is>
-          <t>Performanse 6-34 60ml 0-634</t>
+          <t>Performanse 6-34 60мл 0-634</t>
         </is>
       </c>
       <c r="C636" s="32" t="n">
@@ -12768,7 +12780,7 @@
     <row r="637">
       <c r="B637" s="7" t="inlineStr">
         <is>
-          <t>Performanse 6-77 60ml 0-677</t>
+          <t>Performanse 6-77 60мл 0-677</t>
         </is>
       </c>
       <c r="C637" s="8" t="n">
@@ -12787,7 +12799,7 @@
     <row r="638">
       <c r="B638" s="31" t="inlineStr">
         <is>
-          <t>Performanse 7-00 60ml 0-700</t>
+          <t>Performanse 7-00 60мл 0-700</t>
         </is>
       </c>
       <c r="C638" s="32" t="n">
@@ -12806,7 +12818,7 @@
     <row r="639">
       <c r="B639" s="31" t="inlineStr">
         <is>
-          <t>Performanse 7-09 60ml 0-709</t>
+          <t>Performanse 7-09 60мл 0-709</t>
         </is>
       </c>
       <c r="C639" s="32" t="n">
@@ -12825,7 +12837,7 @@
     <row r="640">
       <c r="B640" s="7" t="inlineStr">
         <is>
-          <t>Performanse 7-12 60ml 0-712</t>
+          <t>Performanse 7-12 60мл 0-712</t>
         </is>
       </c>
       <c r="C640" s="8" t="n">
@@ -12844,7 +12856,7 @@
     <row r="641">
       <c r="B641" s="31" t="inlineStr">
         <is>
-          <t>Performanse 7-3 60ml 0-73</t>
+          <t>Performanse 7-3 60мл 0-73</t>
         </is>
       </c>
       <c r="C641" s="32" t="n">
@@ -12863,7 +12875,7 @@
     <row r="642">
       <c r="B642" s="31" t="inlineStr">
         <is>
-          <t>Performanse 7-4 60ml 0-74</t>
+          <t>Performanse 7-4 60мл 0-74</t>
         </is>
       </c>
       <c r="C642" s="32" t="n">
@@ -12882,7 +12894,7 @@
     <row r="643">
       <c r="B643" s="7" t="inlineStr">
         <is>
-          <t>Performanse 7-6 60ml 0-76</t>
+          <t>Performanse 7-6 60мл 0-76</t>
         </is>
       </c>
       <c r="C643" s="8" t="n">
@@ -12901,7 +12913,7 @@
     <row r="644">
       <c r="B644" s="31" t="inlineStr">
         <is>
-          <t>Performanse 7-71 60ml 0-771</t>
+          <t>Performanse 7-71 60мл 0-771</t>
         </is>
       </c>
       <c r="C644" s="32" t="n">
@@ -12920,7 +12932,7 @@
     <row r="645">
       <c r="B645" s="31" t="inlineStr">
         <is>
-          <t>Performanse 7-75 60ml 0-775</t>
+          <t>Performanse 7-75 60мл 0-775</t>
         </is>
       </c>
       <c r="C645" s="32" t="n">
@@ -12939,7 +12951,7 @@
     <row r="646">
       <c r="B646" s="7" t="inlineStr">
         <is>
-          <t>Performanse 8-0  60ml 0-80</t>
+          <t>Performanse 8-0 60мл 0-80</t>
         </is>
       </c>
       <c r="C646" s="8" t="n">
@@ -12958,7 +12970,7 @@
     <row r="647">
       <c r="B647" s="31" t="inlineStr">
         <is>
-          <t>Performanse 8-12 60ml 0-812</t>
+          <t>Performanse 8-12 60мл 0-812</t>
         </is>
       </c>
       <c r="C647" s="32" t="n">
@@ -12977,7 +12989,7 @@
     <row r="648">
       <c r="B648" s="31" t="inlineStr">
         <is>
-          <t>Performanse 8-34  60ml 0-834</t>
+          <t>Performanse 8-34 60мл 0-834</t>
         </is>
       </c>
       <c r="C648" s="32" t="n">
@@ -12996,7 +13008,7 @@
     <row r="649">
       <c r="B649" s="31" t="inlineStr">
         <is>
-          <t>Performanse 8-43  60ml 0-843</t>
+          <t>Performanse 8-43 60мл 0-843</t>
         </is>
       </c>
       <c r="C649" s="32" t="n">
@@ -13015,7 +13027,7 @@
     <row r="650">
       <c r="B650" s="31" t="inlineStr">
         <is>
-          <t>Performanse 8-44  60ml 0-844</t>
+          <t>Performanse 8-44 60мл 0-844</t>
         </is>
       </c>
       <c r="C650" s="32" t="n">
@@ -13034,7 +13046,7 @@
     <row r="651">
       <c r="B651" s="31" t="inlineStr">
         <is>
-          <t>Performanse 8-6  60ml 0-86</t>
+          <t>Performanse 8-6 60мл 0-86</t>
         </is>
       </c>
       <c r="C651" s="32" t="n">
@@ -13053,7 +13065,7 @@
     <row r="652">
       <c r="B652" s="31" t="inlineStr">
         <is>
-          <t>Performanse 8-71 60ml 0-871</t>
+          <t>Performanse 8-71 60мл 0-871</t>
         </is>
       </c>
       <c r="C652" s="32" t="n">
@@ -13072,7 +13084,7 @@
     <row r="653">
       <c r="B653" s="31" t="inlineStr">
         <is>
-          <t>Performanse 8-72 60ml 0-872</t>
+          <t>Performanse 8-72 60мл 0-872</t>
         </is>
       </c>
       <c r="C653" s="32" t="n">
@@ -13091,7 +13103,7 @@
     <row r="654">
       <c r="B654" s="31" t="inlineStr">
         <is>
-          <t>Performanse 8-73 60ml 0-873</t>
+          <t>Performanse 8-73 60мл 0-873</t>
         </is>
       </c>
       <c r="C654" s="32" t="n">
@@ -13110,7 +13122,7 @@
     <row r="655">
       <c r="B655" s="31" t="inlineStr">
         <is>
-          <t>Performanse 8-8 60ml 0-88</t>
+          <t>Performanse 8-8 60мл 0-88</t>
         </is>
       </c>
       <c r="C655" s="32" t="n">
@@ -13129,7 +13141,7 @@
     <row r="656">
       <c r="B656" s="31" t="inlineStr">
         <is>
-          <t>Performanse 9-03 60ml 0-903</t>
+          <t>Performanse 9-03 60мл 0-903</t>
         </is>
       </c>
       <c r="C656" s="32" t="n">
@@ -13148,7 +13160,7 @@
     <row r="657">
       <c r="B657" s="31" t="inlineStr">
         <is>
-          <t>Performanse 9-12 60ml 0-912</t>
+          <t>Performanse 9-12 60мл 0-912</t>
         </is>
       </c>
       <c r="C657" s="32" t="n">
@@ -13167,7 +13179,7 @@
     <row r="658">
       <c r="B658" s="31" t="inlineStr">
         <is>
-          <t>Performanse 9-26 60ml 0-926</t>
+          <t>Performanse 9-26 60мл 0-926</t>
         </is>
       </c>
       <c r="C658" s="32" t="n">
@@ -13186,7 +13198,7 @@
     <row r="659">
       <c r="B659" s="31" t="inlineStr">
         <is>
-          <t>Performanse 9-3 60ml 0-93</t>
+          <t>Performanse 9-3 60мл 0-93</t>
         </is>
       </c>
       <c r="C659" s="32" t="n">
@@ -13205,7 +13217,7 @@
     <row r="660">
       <c r="B660" s="31" t="inlineStr">
         <is>
-          <t>Performanse 9-31  60ml 0-931</t>
+          <t>Performanse 9-31 60мл 0-931</t>
         </is>
       </c>
       <c r="C660" s="32" t="n">
@@ -13224,7 +13236,7 @@
     <row r="661">
       <c r="B661" s="31" t="inlineStr">
         <is>
-          <t>Performanse 9-7  60ml 0-97</t>
+          <t>Performanse 9-7 60мл 0-97</t>
         </is>
       </c>
       <c r="C661" s="32" t="n">
@@ -13243,7 +13255,7 @@
     <row r="662">
       <c r="B662" s="31" t="inlineStr">
         <is>
-          <t>Performanse 9-72  60ml 0-972</t>
+          <t>Performanse 9-72 60мл 0-972</t>
         </is>
       </c>
       <c r="C662" s="32" t="n">
@@ -13262,7 +13274,7 @@
     <row r="663">
       <c r="B663" s="31" t="inlineStr">
         <is>
-          <t>Performanse 9-8  60ml 0-98</t>
+          <t>Performanse 9-8 60мл 0-98</t>
         </is>
       </c>
       <c r="C663" s="32" t="n">
@@ -13281,7 +13293,7 @@
     <row r="664">
       <c r="B664" s="7" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 0/01 60 мл 00-01</t>
+          <t>Silk Touch Безаммиачный стойкая краска 0/01 60мл 00-01</t>
         </is>
       </c>
       <c r="C664" s="8" t="n">
@@ -13300,7 +13312,7 @@
     <row r="665">
       <c r="B665" s="7" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 10/7 60 мл 010-7</t>
+          <t>Silk Touch Безаммиачный стойкая краска 10/7 60мл 010-7</t>
         </is>
       </c>
       <c r="C665" s="8" t="n">
@@ -13319,7 +13331,7 @@
     <row r="666">
       <c r="B666" s="7" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 10/73 60 мл 010-73</t>
+          <t>Silk Touch Безаммиачный стойкая краска 10/73 60мл 010-73</t>
         </is>
       </c>
       <c r="C666" s="8" t="n">
@@ -13338,7 +13350,7 @@
     <row r="667">
       <c r="B667" s="7" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 6/0 60 мл 06-0</t>
+          <t>Silk Touch Безаммиачный стойкая краска 6/0 60мл 06-0</t>
         </is>
       </c>
       <c r="C667" s="8" t="n">
@@ -13357,7 +13369,7 @@
     <row r="668">
       <c r="B668" s="7" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 7/0 60 мл 07-0</t>
+          <t>Silk Touch Безаммиачный стойкая краска 7/0 60мл 07-0</t>
         </is>
       </c>
       <c r="C668" s="8" t="n">
@@ -13376,7 +13388,7 @@
     <row r="669">
       <c r="B669" s="31" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 8/72 60 мл 08-72</t>
+          <t>Silk Touch Безаммиачный стойкая краска 8/72 60мл 08-72</t>
         </is>
       </c>
       <c r="C669" s="32" t="n">
@@ -13395,7 +13407,7 @@
     <row r="670">
       <c r="B670" s="31" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 9/0 60 мл 09-0</t>
+          <t>Silk Touch Безаммиачный стойкая краска 9/0 60мл 09-0</t>
         </is>
       </c>
       <c r="C670" s="32" t="n">
@@ -13414,7 +13426,7 @@
     <row r="671">
       <c r="B671" s="7" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 9/25 60 мл 09-25</t>
+          <t>Silk Touch Безаммиачный стойкая краска 9/25 60мл 09-25</t>
         </is>
       </c>
       <c r="C671" s="8" t="n">
@@ -13433,7 +13445,7 @@
     <row r="672">
       <c r="B672" s="7" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 9/26 60 мл 09-26</t>
+          <t>Silk Touch Безаммиачный стойкая краска 9/26 60мл 09-26</t>
         </is>
       </c>
       <c r="C672" s="8" t="n">
@@ -13452,7 +13464,7 @@
     <row r="673">
       <c r="B673" s="7" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 9/31 60 мл 09-31</t>
+          <t>Silk Touch Безаммиачный стойкая краска 9/31 60мл 09-31</t>
         </is>
       </c>
       <c r="C673" s="8" t="n">
@@ -13471,7 +13483,7 @@
     <row r="674">
       <c r="B674" s="7" t="inlineStr">
         <is>
-          <t>Silk Touch Безаммиачный стойкая краска 9/43 60 мл 09-43</t>
+          <t>Silk Touch Безаммиачный стойкая краска 9/43 60мл 09-43</t>
         </is>
       </c>
       <c r="C674" s="8" t="n">
@@ -13490,7 +13502,7 @@
     <row r="675" ht="22.5" customHeight="1">
       <c r="B675" s="7" t="inlineStr">
         <is>
-          <t>Бальзам SB питание и восст. для волос с маслом семян льна 1000мл 773205</t>
+          <t>Бальзам SB питание и восстановления для волос с маслом семян льна 1000мл 773205</t>
         </is>
       </c>
       <c r="C675" s="8" t="n">
@@ -13509,7 +13521,7 @@
     <row r="676">
       <c r="B676" s="7" t="inlineStr">
         <is>
-          <t>Бальзам SL д/увлажнения волос 1000 мл. 726796</t>
+          <t>Бальзам SL для увлажнения волос 1000мл 726796</t>
         </is>
       </c>
       <c r="C676" s="8" t="n">
@@ -13528,7 +13540,7 @@
     <row r="677">
       <c r="B677" s="7" t="inlineStr">
         <is>
-          <t>Бальзам SL д/увлажнения волос 5000 мл. 726857</t>
+          <t>Бальзам SL для увлажнения волос 5000мл 726857</t>
         </is>
       </c>
       <c r="C677" s="10" t="n">
@@ -13547,7 +13559,7 @@
     <row r="678">
       <c r="B678" s="7" t="inlineStr">
         <is>
-          <t>Гель д/удаления краски с кожи, 150 мл. 726703</t>
+          <t>Гель для удаления краски с кожи 150мл 726703</t>
         </is>
       </c>
       <c r="C678" s="8" t="n">
@@ -13566,7 +13578,7 @@
     <row r="679">
       <c r="B679" s="7" t="inlineStr">
         <is>
-          <t>Конд. CARE 2-е увл. 1000 мл. 395478</t>
+          <t>Кондиционер CARE двойное увлажнения 1000мл 395478</t>
         </is>
       </c>
       <c r="C679" s="8" t="n">
@@ -13585,7 +13597,7 @@
     <row r="680">
       <c r="B680" s="7" t="inlineStr">
         <is>
-          <t>Конд. CARE ULTIMATE д/восст. структуры волос 1000 мл. 772338</t>
+          <t>Кондиционер CARE ULTIMATE для восстановления структуры волос 1000мл 772338</t>
         </is>
       </c>
       <c r="C680" s="8" t="n">
@@ -13604,7 +13616,7 @@
     <row r="681">
       <c r="B681" s="7" t="inlineStr">
         <is>
-          <t>Конд. CARE ULTIMATE д/окрашенных волос 1000 мл. 772369</t>
+          <t>Кондиционер CARE ULTIMATE для окрашенных волос 1000мл 772369</t>
         </is>
       </c>
       <c r="C681" s="8" t="n">
@@ -13623,7 +13635,7 @@
     <row r="682">
       <c r="B682" s="7" t="inlineStr">
         <is>
-          <t>Конд. CARE д/восст. структуры волос 1000 мл. 395195</t>
+          <t>Кондиционер CARE для восстановления структуры волос 1000мл 395195</t>
         </is>
       </c>
       <c r="C682" s="8" t="n">
@@ -13642,7 +13654,7 @@
     <row r="683">
       <c r="B683" s="7" t="inlineStr">
         <is>
-          <t>Конд. CARE д/ежедневного применения 1000 мл. 772277</t>
+          <t>Кондиционер CARE для ежедневного применения 1000мл 772277</t>
         </is>
       </c>
       <c r="C683" s="8" t="n">
@@ -13661,7 +13673,7 @@
     <row r="684">
       <c r="B684" s="7" t="inlineStr">
         <is>
-          <t>Конд. CARE д/окрашенных волос 1000 мл. 395072</t>
+          <t>Кондиционер CARE для окрашенных волос 1000мл 395072</t>
         </is>
       </c>
       <c r="C684" s="8" t="n">
@@ -13680,7 +13692,7 @@
     <row r="685" ht="22.5" customHeight="1">
       <c r="B685" s="7" t="inlineStr">
         <is>
-          <t>Кондиционер SALON BEAUTY для волос с коллагеном 1000 мл 775155</t>
+          <t>Кондиционер SB для волос с коллагеном 1000мл 775155</t>
         </is>
       </c>
       <c r="C685" s="8" t="n">
@@ -13699,7 +13711,7 @@
     <row r="686" ht="22.5" customHeight="1">
       <c r="B686" s="7" t="inlineStr">
         <is>
-          <t>Конд. SB для окр.волос с маслом виноградной косточки 1000мл 773151</t>
+          <t>Кондиционер SB для окрашенных волос с маслом виноградной косточки 1000мл 773151</t>
         </is>
       </c>
       <c r="C686" s="8" t="n">
@@ -13718,7 +13730,7 @@
     <row r="687" ht="22.5" customHeight="1">
       <c r="B687" s="7" t="inlineStr">
         <is>
-          <t>Конд. SB увл. и гладкость для волос с экстрактом ламинарии 1000мл 773175</t>
+          <t>Кондиционер SB увлажнение и гладкость для волос с экстрактом ламинарии 1000мл 773175</t>
         </is>
       </c>
       <c r="C687" s="8" t="n">
@@ -13737,7 +13749,7 @@
     <row r="688">
       <c r="B688" s="7" t="inlineStr">
         <is>
-          <t>Конд. SL д/ежедневного прим. PH 5.5 1000 мл. 726833</t>
+          <t>Кондиционер SL для ежедневного применения PH 5.5 1000мл 726833</t>
         </is>
       </c>
       <c r="C688" s="8" t="n">
@@ -13756,7 +13768,7 @@
     <row r="689">
       <c r="B689" s="7" t="inlineStr">
         <is>
-          <t>Конд.-стабилиз. SL цв. рн 3,5, 1000 мл. 726789</t>
+          <t>Кондиционер-стабилизатор SL рн 3,5 1000мл 726789</t>
         </is>
       </c>
       <c r="C689" s="8" t="n">
@@ -13775,7 +13787,7 @@
     <row r="690">
       <c r="B690" s="7" t="inlineStr">
         <is>
-          <t>Конд.-стабилиз. SL цв. рн 3,5, 5000 мл. 393528</t>
+          <t>Кондиционер-стабилизатор SL рн 3,5 5000мл 393528</t>
         </is>
       </c>
       <c r="C690" s="10" t="n">
@@ -13794,7 +13806,7 @@
     <row r="691">
       <c r="B691" s="7" t="inlineStr">
         <is>
-          <t>краска д/бровей графит (НАБОР) 772529</t>
+          <t>краска для бровей графит (НАБОР) 772529</t>
         </is>
       </c>
       <c r="C691" s="8" t="n">
@@ -13813,7 +13825,7 @@
     <row r="692">
       <c r="B692" s="31" t="inlineStr">
         <is>
-          <t>краска д/бровей иссиня-черный (НАБОР) 772543</t>
+          <t>краска для бровей иссиня-черный (НАБОР) 772543</t>
         </is>
       </c>
       <c r="C692" s="32" t="n">
@@ -13832,7 +13844,7 @@
     <row r="693">
       <c r="B693" s="7" t="inlineStr">
         <is>
-          <t>краска д/бровей коричневая (НАБОР) 772512/729193</t>
+          <t>краска для бровей коричневая (НАБОР) 772512/729193</t>
         </is>
       </c>
       <c r="C693" s="8" t="n">
@@ -13851,7 +13863,7 @@
     <row r="694">
       <c r="B694" s="7" t="inlineStr">
         <is>
-          <t>краска д/бровей коричневая 20 мл 772444</t>
+          <t>краска для бровей коричневая 20мл 772444</t>
         </is>
       </c>
       <c r="C694" s="8" t="n">
@@ -13870,7 +13882,7 @@
     <row r="695">
       <c r="B695" s="31" t="inlineStr">
         <is>
-          <t>краска д/бровей темный графит 20 мл VISION 772482</t>
+          <t>краска для бровей темный графит 20мл VISION 772482</t>
         </is>
       </c>
       <c r="C695" s="32" t="n">
@@ -13889,7 +13901,7 @@
     <row r="696">
       <c r="B696" s="7" t="inlineStr">
         <is>
-          <t>краска д/бровей черная (НАБОР) 772505</t>
+          <t>краска для бровей черная (НАБОР) 772505</t>
         </is>
       </c>
       <c r="C696" s="8" t="n">
@@ -13927,7 +13939,7 @@
     <row r="698" ht="22.5" customHeight="1">
       <c r="B698" s="7" t="inlineStr">
         <is>
-          <t>Крем - флюид 15 в 1 (Ollin Perfect Hair Leave-in Cream-Fluid) – 250 мл 773304</t>
+          <t>Крем - флюид 15 в 1 (Ollin Perfect Hair Leave-in Cream-Fluid) – 250мл 773304</t>
         </is>
       </c>
       <c r="C698" s="8" t="n">
@@ -13946,7 +13958,7 @@
     <row r="699">
       <c r="B699" s="7" t="inlineStr">
         <is>
-          <t>Лак STYLE СФ, 500 мл. 731090/393177</t>
+          <t>Лак STYLE сильной фиксации 500мл 731090/393177</t>
         </is>
       </c>
       <c r="C699" s="8" t="n">
@@ -13965,7 +13977,7 @@
     <row r="700">
       <c r="B700" s="7" t="inlineStr">
         <is>
-          <t>Лак STYLE УСФ без отдушки 400мл 971274/391913</t>
+          <t>Лак STYLE ультрасильной фиксации без отдушки 400мл 971274/391913</t>
         </is>
       </c>
       <c r="C700" s="8" t="n">
@@ -14003,7 +14015,7 @@
     <row r="702">
       <c r="B702" s="31" t="inlineStr">
         <is>
-          <t>Маска CARE д/окрашенных волос 200 мл 395119</t>
+          <t>Маска CARE для окрашенных волос 200мл 395119</t>
         </is>
       </c>
       <c r="C702" s="32" t="n">
@@ -14022,7 +14034,7 @@
     <row r="703">
       <c r="B703" s="7" t="inlineStr">
         <is>
-          <t>Маска SB для волос с коллагеном  500 мл 775162</t>
+          <t>Маска SB для волос с коллагеном 500мл 775162</t>
         </is>
       </c>
       <c r="C703" s="8" t="n">
@@ -14060,7 +14072,7 @@
     <row r="705">
       <c r="B705" s="7" t="inlineStr">
         <is>
-          <t>Оксид (СЕРЫЙ) 1,5%, 1000 мл. 397588</t>
+          <t>Оксид (СЕРЫЙ) 1,5% 1000мл 397588</t>
         </is>
       </c>
       <c r="C705" s="8" t="n">
@@ -14079,7 +14091,7 @@
     <row r="706">
       <c r="B706" s="31" t="inlineStr">
         <is>
-          <t>Оксид (СЕРЫЙ) 1,5%, 90 мл. 397519</t>
+          <t>Оксид (СЕРЫЙ) 1,5% 90мл 397519</t>
         </is>
       </c>
       <c r="C706" s="32" t="n">
@@ -14098,7 +14110,7 @@
     <row r="707">
       <c r="B707" s="7" t="inlineStr">
         <is>
-          <t>Оксид (СЕРЫЙ) 12%, 1000 мл. 397625</t>
+          <t>Оксид (СЕРЫЙ) 12% 1000мл 397625</t>
         </is>
       </c>
       <c r="C707" s="8" t="n">
@@ -14117,7 +14129,7 @@
     <row r="708">
       <c r="B708" s="7" t="inlineStr">
         <is>
-          <t>Оксид (СЕРЫЙ) 3%, 1000 мл. 397595</t>
+          <t>Оксид (СЕРЫЙ) 3% 1000мл 397595</t>
         </is>
       </c>
       <c r="C708" s="8" t="n">
@@ -14136,7 +14148,7 @@
     <row r="709">
       <c r="B709" s="7" t="inlineStr">
         <is>
-          <t>Оксид (СЕРЫЙ) 6%, 1000 мл. 397601</t>
+          <t>Оксид (СЕРЫЙ) 6% 1000мл 397601</t>
         </is>
       </c>
       <c r="C709" s="8" t="n">
@@ -14155,7 +14167,7 @@
     <row r="710">
       <c r="B710" s="7" t="inlineStr">
         <is>
-          <t>Оксид (СЕРЫЙ) 9%, 1000 мл. 397618/728691</t>
+          <t>Оксид (СЕРЫЙ) 9% 1000мл 397618/728691</t>
         </is>
       </c>
       <c r="C710" s="8" t="n">
@@ -14174,7 +14186,7 @@
     <row r="711">
       <c r="B711" s="7" t="inlineStr">
         <is>
-          <t>Оксид Silk Touch 6% 1000 мл. 729049</t>
+          <t>Оксид Silk Touch 6% 1000мл 729049</t>
         </is>
       </c>
       <c r="C711" s="8" t="n">
@@ -14193,7 +14205,7 @@
     <row r="712">
       <c r="B712" s="7" t="inlineStr">
         <is>
-          <t>Спрей термозащитный д/волос 250мл 772383</t>
+          <t>Спрей термозащитный для волос 250мл 772383</t>
         </is>
       </c>
       <c r="C712" s="8" t="n">
@@ -14212,7 +14224,7 @@
     <row r="713">
       <c r="B713" s="7" t="inlineStr">
         <is>
-          <t>Спрей-объем "Морская соль" 250 мл. 394792</t>
+          <t>Спрей-объём "Морская соль" 250мл 394792</t>
         </is>
       </c>
       <c r="C713" s="8" t="n">
@@ -14231,7 +14243,7 @@
     <row r="714">
       <c r="B714" s="31" t="inlineStr">
         <is>
-          <t>Супра Blond Powder NO Aroma (голубой порошок) 30 г. 721548</t>
+          <t>Супра Blond Powder NO Aroma (голубой порошок) 30г 721548</t>
         </is>
       </c>
       <c r="C714" s="32" t="n">
@@ -14250,7 +14262,7 @@
     <row r="715">
       <c r="B715" s="7" t="inlineStr">
         <is>
-          <t>Супра Blond Powder NO Aroma (голубой порошок) 500 г. 728998</t>
+          <t>Супра Blond Powder NO Aroma (голубой порошок) 500г 728998</t>
         </is>
       </c>
       <c r="C715" s="8" t="n">
@@ -14269,7 +14281,7 @@
     <row r="716">
       <c r="B716" s="7" t="inlineStr">
         <is>
-          <t>Супра Performanse (белый порошок) 500 г 729971</t>
+          <t>Супра Performanse (белый порошок) 500г 729971</t>
         </is>
       </c>
       <c r="C716" s="8" t="n">
@@ -14288,7 +14300,7 @@
     <row r="717">
       <c r="B717" s="7" t="inlineStr">
         <is>
-          <t>Супра Performanse Open Tech д/открытых техник 500г 771959</t>
+          <t>Супра Performanse Open Tech для открытых техник 500г 771959</t>
         </is>
       </c>
       <c r="C717" s="10" t="n">
@@ -14307,7 +14319,7 @@
     <row r="718">
       <c r="B718" s="7" t="inlineStr">
         <is>
-          <t>Супра с аром. лаванды, саше 30 г. Blond Powder 721531</t>
+          <t>Супра с ароматом лаванды, саше 30г Blond Powder 721531</t>
         </is>
       </c>
       <c r="C718" s="8" t="n">
@@ -14326,7 +14338,7 @@
     <row r="719">
       <c r="B719" s="7" t="inlineStr">
         <is>
-          <t>Флюид BIONIKA реконструктор 100 мл. 397229</t>
+          <t>Флюид BIONIKA реконструктор 100мл 397229</t>
         </is>
       </c>
       <c r="C719" s="8" t="n">
@@ -14345,7 +14357,7 @@
     <row r="720">
       <c r="B720" s="7" t="inlineStr">
         <is>
-          <t>Шампунь CARE ULTIMATE увл. 1000 мл. 772291</t>
+          <t>Шампунь CARE ULTIMATE увлажения волос 1000мл 772291</t>
         </is>
       </c>
       <c r="C720" s="10" t="n">
@@ -14364,7 +14376,7 @@
     <row r="721">
       <c r="B721" s="7" t="inlineStr">
         <is>
-          <t>Шампунь CARE д/восст. структуры волос 1000 мл. 395157</t>
+          <t>Шампунь CARE для восстановления структуры волос 1000мл 395157</t>
         </is>
       </c>
       <c r="C721" s="8" t="n">
@@ -14383,7 +14395,7 @@
     <row r="722">
       <c r="B722" s="7" t="inlineStr">
         <is>
-          <t>Шампунь CARE д/ежедневного применения 1000 мл. 772260</t>
+          <t>Шампунь CARE для ежедневного применения 1000мл 772260</t>
         </is>
       </c>
       <c r="C722" s="8" t="n">
@@ -14402,7 +14414,7 @@
     <row r="723">
       <c r="B723" s="7" t="inlineStr">
         <is>
-          <t>Шампунь CARE д/объема волос 1000 мл. 395355</t>
+          <t>Шампунь CARE для объёма волос 1000мл 395355</t>
         </is>
       </c>
       <c r="C723" s="8" t="n">
@@ -14421,7 +14433,7 @@
     <row r="724">
       <c r="B724" s="7" t="inlineStr">
         <is>
-          <t>Шампунь CARE д/окрашенных волос 1000 мл. 395034</t>
+          <t>Шампунь CARE для окрашенных волос 1000мл 395034</t>
         </is>
       </c>
       <c r="C724" s="8" t="n">
@@ -14440,7 +14452,7 @@
     <row r="725">
       <c r="B725" s="31" t="inlineStr">
         <is>
-          <t>Шампунь CARE с маслом миндаля 1000 мл. 395515</t>
+          <t>Шампунь CARE с маслом миндаля 1000мл 395515</t>
         </is>
       </c>
       <c r="C725" s="32" t="n">
@@ -14459,7 +14471,7 @@
     <row r="726">
       <c r="B726" s="7" t="inlineStr">
         <is>
-          <t>Шампунь CARE увлажняющий 1000 мл. 395416</t>
+          <t>Шампунь CARE увлажняющий 1000мл 395416</t>
         </is>
       </c>
       <c r="C726" s="8" t="n">
@@ -14478,7 +14490,7 @@
     <row r="727">
       <c r="B727" s="31" t="inlineStr">
         <is>
-          <t>Шампунь CARE увлажняющий 250 мл. 395430</t>
+          <t>Шампунь CARE увлажняющий 250мл 395430</t>
         </is>
       </c>
       <c r="C727" s="32" t="n">
@@ -14497,7 +14509,7 @@
     <row r="728">
       <c r="B728" s="7" t="inlineStr">
         <is>
-          <t>Шампунь MEN д/волос и тела освежающий 1000мл 729759</t>
+          <t>Шампунь MEN для волос и тела освежающий 1000мл 729759</t>
         </is>
       </c>
       <c r="C728" s="8" t="n">
@@ -14516,7 +14528,7 @@
     <row r="729">
       <c r="B729" s="31" t="inlineStr">
         <is>
-          <t>Шампунь MEN д/волос и тела освежающий 250 мл. 725485/723207</t>
+          <t>Шампунь MEN для волос и тела освежающий 250мл 725485/723207</t>
         </is>
       </c>
       <c r="C729" s="32" t="n">
@@ -14535,7 +14547,7 @@
     <row r="730">
       <c r="B730" s="7" t="inlineStr">
         <is>
-          <t>Шампунь MP на основе черного риса 1000 мл. 774103</t>
+          <t>Шампунь MP на основе черного риса 1000мл 774103</t>
         </is>
       </c>
       <c r="C730" s="10" t="n">
@@ -14554,7 +14566,7 @@
     <row r="731">
       <c r="B731" s="7" t="inlineStr">
         <is>
-          <t>Шампунь SB  для  волос  с коллагеном 1000 мл 775148</t>
+          <t>Шампунь SB для волос с коллагеном 1000мл 775148</t>
         </is>
       </c>
       <c r="C731" s="8" t="n">
@@ -14573,7 +14585,7 @@
     <row r="732">
       <c r="B732" s="7" t="inlineStr">
         <is>
-          <t>Шампунь SB для окр. волос с экстрактом винограда 1000мл 773144</t>
+          <t>Шампунь SB для окрашенных волос с экстрактом винограда 1000мл 773144</t>
         </is>
       </c>
       <c r="C732" s="8" t="n">
@@ -14592,7 +14604,7 @@
     <row r="733" ht="22.5" customHeight="1">
       <c r="B733" s="7" t="inlineStr">
         <is>
-          <t>Шампунь SB питат. для волос с экстрактом семян льна 1000мл 773199</t>
+          <t>Шампунь SB питательный для волос с экстрактом семян льна 1000мл 773199</t>
         </is>
       </c>
       <c r="C733" s="8" t="n">
@@ -14611,7 +14623,7 @@
     <row r="734" ht="22.5" customHeight="1">
       <c r="B734" s="7" t="inlineStr">
         <is>
-          <t>Шампунь SB увл. для волос с экстрактом ламинарии 1000мл 773168</t>
+          <t>Шампунь SB увлажнения для волос с экстрактом ламинарии 1000мл 773168</t>
         </is>
       </c>
       <c r="C734" s="8" t="n">
@@ -14630,7 +14642,7 @@
     <row r="735">
       <c r="B735" s="7" t="inlineStr">
         <is>
-          <t>Шампунь SL д/ежедневного прим. PH 5.5 1000 мл. 726802/721999</t>
+          <t>Шампунь SL для ежедневного применения PH 5.5 1000мл 726802/721999</t>
         </is>
       </c>
       <c r="C735" s="8" t="n">
@@ -14649,7 +14661,7 @@
     <row r="736">
       <c r="B736" s="7" t="inlineStr">
         <is>
-          <t>Шампунь SL д/ежедневного прим. PH 5.5 5000 мл. 726864</t>
+          <t>Шампунь SL для ежедневного применения PH 5.5 5000мл 726864</t>
         </is>
       </c>
       <c r="C736" s="10" t="n">
@@ -14668,7 +14680,7 @@
     <row r="737">
       <c r="B737" s="7" t="inlineStr">
         <is>
-          <t>Шампунь SL д/холодных оттенков 1000 мл. 728912</t>
+          <t>Шампунь SL для холодных оттенков 1000мл 728912</t>
         </is>
       </c>
       <c r="C737" s="8" t="n">
@@ -14687,7 +14699,7 @@
     <row r="738">
       <c r="B738" s="7" t="inlineStr">
         <is>
-          <t>Шампунь-пилинг SL РН 7.0, 1000 мл. 726819</t>
+          <t>Шампунь-пилинг SL РН 7.0 1000мл 726819</t>
         </is>
       </c>
       <c r="C738" s="8" t="n">
@@ -14706,7 +14718,7 @@
     <row r="739">
       <c r="B739" s="7" t="inlineStr">
         <is>
-          <t>Шампунь-стабилиз. SL цв. рн 3,5, 1000 мл. 726826</t>
+          <t>Шампунь-стабилизирующий SL рн 3,5 1000мл 726826</t>
         </is>
       </c>
       <c r="C739" s="8" t="n">
@@ -14725,7 +14737,7 @@
     <row r="740">
       <c r="B740" s="7" t="inlineStr">
         <is>
-          <t>Шампунь-стабилиз. SL цв. рн 3,5, 5000 мл. 393481</t>
+          <t>Шампунь-стабилизирующий SL рн 3,5 5000мл 393481</t>
         </is>
       </c>
       <c r="C740" s="10" t="n">
@@ -14747,10 +14759,10 @@
           <t>SCHWARZKOPF</t>
         </is>
       </c>
-      <c r="C741" s="16" t="n"/>
+      <c r="C741" s="43" t="n"/>
       <c r="D741" s="24" t="n"/>
-      <c r="E741" s="25" t="n"/>
-      <c r="F741" s="26" t="n"/>
+      <c r="E741" s="24" t="n"/>
+      <c r="F741" s="44" t="n"/>
     </row>
     <row r="742" ht="28.5" customHeight="1">
       <c r="B742" s="12" t="inlineStr">
@@ -14758,10 +14770,10 @@
           <t>IGORA/BLONDME - Красители и специальные продукты</t>
         </is>
       </c>
-      <c r="C742" s="17" t="n"/>
+      <c r="C742" s="45" t="n"/>
       <c r="D742" s="24" t="n"/>
-      <c r="E742" s="25" t="n"/>
-      <c r="F742" s="37" t="n"/>
+      <c r="E742" s="24" t="n"/>
+      <c r="F742" s="44" t="n"/>
     </row>
     <row r="743">
       <c r="B743" s="31" t="inlineStr">
@@ -14823,7 +14835,7 @@
     <row r="746" ht="22.5" customHeight="1">
       <c r="B746" s="7" t="inlineStr">
         <is>
-          <t>NS Лосьон д/химической завивки для трудных волос №0 1000мл 1969344</t>
+          <t>NS Лосьон для химической завивки для трудных волос №0 1000мл 1969344</t>
         </is>
       </c>
       <c r="C746" s="10" t="n">
@@ -14842,7 +14854,7 @@
     <row r="747" ht="22.5" customHeight="1">
       <c r="B747" s="31" t="inlineStr">
         <is>
-          <t>NS Лосьон д/химической завивки нормальных волос №1 1000мл 1969343</t>
+          <t>NS Лосьон для химической завивки нормальных волос №1 1000мл 1969343</t>
         </is>
       </c>
       <c r="C747" s="36" t="n">
@@ -14861,7 +14873,7 @@
     <row r="748" ht="22.5" customHeight="1">
       <c r="B748" s="31" t="inlineStr">
         <is>
-          <t>NS Лосьон д/химической завивки окрашенных волос №2 1000мл 1969347</t>
+          <t>NS Лосьон для химической завивки окрашенных волос №2 1000мл 1969347</t>
         </is>
       </c>
       <c r="C748" s="36" t="n">
@@ -14918,7 +14930,7 @@
     <row r="751" ht="22.5" customHeight="1">
       <c r="B751" s="7" t="inlineStr">
         <is>
-          <t>Игора Варио Блонд SUPER PLUS (СИНЯЯ БАНКА 8+) 450 (НОВЫЙ ДИЗАЙН!) 2242115new</t>
+          <t>Игора Варио Блонд SUPER PLUS (СИНЯЯ БАНКА 8+) 450 2242115new</t>
         </is>
       </c>
       <c r="C751" s="10" t="n">
@@ -14937,7 +14949,7 @@
     <row r="752">
       <c r="B752" s="7" t="inlineStr">
         <is>
-          <t>Краска IR 0-00 Клир 60мл 60мл и000</t>
+          <t>Краска IR 0-00 Клир 60мл и000</t>
         </is>
       </c>
       <c r="C752" s="8" t="n">
@@ -15925,7 +15937,7 @@
     <row r="804" ht="22.5" customHeight="1">
       <c r="B804" s="7" t="inlineStr">
         <is>
-          <t>Краска IR AB 4-60 Средний коричневый шоколадный натурал. 60мл и460</t>
+          <t>Краска IR AB 4-60 Средний коричневый шоколадный натуральный 60мл и460</t>
         </is>
       </c>
       <c r="C804" s="8" t="n">
@@ -16305,7 +16317,7 @@
     <row r="824" ht="22.5" customHeight="1">
       <c r="B824" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 10-21 Экстрасветлый блондин пепельн. сандрэ 60мл и1021</t>
+          <t>Краска IR HL 10-21 Экстрасветлый блондин пепельный сандрэ 60мл и1021</t>
         </is>
       </c>
       <c r="C824" s="8" t="n">
@@ -16343,7 +16355,7 @@
     <row r="826">
       <c r="B826" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 12-0 Спец. блондин натуральный 60мл и120</t>
+          <t>Краска IR HL 12-0 Специальный блондин натуральный 60мл и120</t>
         </is>
       </c>
       <c r="C826" s="8" t="n">
@@ -16362,7 +16374,7 @@
     <row r="827">
       <c r="B827" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 12-19 Спец. блондин фиолетовый сандрэ 60мл и1219</t>
+          <t>Краска IR HL 12-19 Специальный блондин фиолетовый сандрэ 60мл и1219</t>
         </is>
       </c>
       <c r="C827" s="8" t="n">
@@ -16381,7 +16393,7 @@
     <row r="828">
       <c r="B828" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 12-2 Спец. блондин пепельный 60мл и122</t>
+          <t>Краска IR HL 12-2 Специальный блондин пепельный 60мл и122</t>
         </is>
       </c>
       <c r="C828" s="8" t="n">
@@ -16400,7 +16412,7 @@
     <row r="829">
       <c r="B829" s="7" t="inlineStr">
         <is>
-          <t>Краска IR HL 12-21 Спец. блондин пепельный сандрэ 60мл и1221</t>
+          <t>Краска IR HL 12-21 Специальный блондин пепельный сандрэ 60мл и1221</t>
         </is>
       </c>
       <c r="C829" s="8" t="n">
@@ -16419,7 +16431,7 @@
     <row r="830">
       <c r="B830" s="7" t="inlineStr">
         <is>
-          <t>Оксигент на масляной основе 12% 1000 мл 2184627</t>
+          <t>Оксигент на масляной основе 12% 1000мл 2184627</t>
         </is>
       </c>
       <c r="C830" s="8" t="n">
@@ -16438,7 +16450,7 @@
     <row r="831">
       <c r="B831" s="31" t="inlineStr">
         <is>
-          <t>Оксигент на масляной основе 3% 1000 мл 2184625</t>
+          <t>Оксигент на масляной основе 3% 1000мл 2184625</t>
         </is>
       </c>
       <c r="C831" s="32" t="n">
@@ -16457,7 +16469,7 @@
     <row r="832">
       <c r="B832" s="31" t="inlineStr">
         <is>
-          <t>Оксигент на масляной основе 6% 1000 мл 2184628</t>
+          <t>Оксигент на масляной основе 6% 1000мл 2184628</t>
         </is>
       </c>
       <c r="C832" s="32" t="n">
@@ -16476,7 +16488,7 @@
     <row r="833">
       <c r="B833" s="31" t="inlineStr">
         <is>
-          <t>Оксигент на масляной основе 9% 1000 мл 1847105</t>
+          <t>Оксигент на масляной основе 9% 1000мл 1847105</t>
         </is>
       </c>
       <c r="C833" s="32" t="n">
@@ -16498,15 +16510,15 @@
           <t>OSIS - Укладка</t>
         </is>
       </c>
-      <c r="C834" s="17" t="n"/>
+      <c r="C834" s="45" t="n"/>
       <c r="D834" s="24" t="n"/>
-      <c r="E834" s="25" t="n"/>
-      <c r="F834" s="37" t="n"/>
+      <c r="E834" s="24" t="n"/>
+      <c r="F834" s="44" t="n"/>
     </row>
     <row r="835">
       <c r="B835" s="31" t="inlineStr">
         <is>
-          <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 300 мл. 1970454</t>
+          <t>Лак для волос №2 фикс. 3+ СФ FREEZE 300мл 1970454</t>
         </is>
       </c>
       <c r="C835" s="32" t="n">
@@ -16525,7 +16537,7 @@
     <row r="836">
       <c r="B836" s="7" t="inlineStr">
         <is>
-          <t>Лак д/волос №2 фикс. 3+ СФ FREEZE 500 мл. 1970621</t>
+          <t>Лак для волос №2 фикс. 3+ СФ FREEZE 500мл 1970621</t>
         </is>
       </c>
       <c r="C836" s="8" t="n">
@@ -16544,7 +16556,7 @@
     <row r="837">
       <c r="B837" s="7" t="inlineStr">
         <is>
-          <t>Спрей с бриллиантовым блеском Sparkler 300 мл. 1970641</t>
+          <t>Спрей с бриллиантовым блеском Sparkler 300мл 1970641</t>
         </is>
       </c>
       <c r="C837" s="8" t="n">
@@ -16566,15 +16578,15 @@
           <t>SILHOUETTE/Professionnelle - Укладка</t>
         </is>
       </c>
-      <c r="C838" s="17" t="n"/>
+      <c r="C838" s="45" t="n"/>
       <c r="D838" s="24" t="n"/>
-      <c r="E838" s="25" t="n"/>
-      <c r="F838" s="37" t="n"/>
+      <c r="E838" s="24" t="n"/>
+      <c r="F838" s="44" t="n"/>
     </row>
     <row r="839">
       <c r="B839" s="7" t="inlineStr">
         <is>
-          <t>Professionnelle Лак СФ  (Венгрия) 500 мл. 8701</t>
+          <t>Professionnelle Лак СФ (Венгрия) 500мл 8701</t>
         </is>
       </c>
       <c r="C839" s="8" t="n">
@@ -16593,7 +16605,7 @@
     <row r="840">
       <c r="B840" s="7" t="inlineStr">
         <is>
-          <t>Гель д/волос сверхсильной фиксации 250мл 2147236</t>
+          <t>Гель для волос сверхсильной фиксации 250мл 2147236</t>
         </is>
       </c>
       <c r="C840" s="8" t="n">
@@ -16634,10 +16646,10 @@
           <t>WELLA</t>
         </is>
       </c>
-      <c r="C842" s="16" t="n"/>
+      <c r="C842" s="43" t="n"/>
       <c r="D842" s="24" t="n"/>
-      <c r="E842" s="25" t="n"/>
-      <c r="F842" s="26" t="n"/>
+      <c r="E842" s="24" t="n"/>
+      <c r="F842" s="44" t="n"/>
     </row>
     <row r="843" ht="14.25" customHeight="1">
       <c r="B843" s="12" t="inlineStr">
@@ -16645,15 +16657,15 @@
           <t>EIMI - Укладка</t>
         </is>
       </c>
-      <c r="C843" s="17" t="n"/>
+      <c r="C843" s="45" t="n"/>
       <c r="D843" s="24" t="n"/>
-      <c r="E843" s="25" t="n"/>
-      <c r="F843" s="37" t="n"/>
+      <c r="E843" s="24" t="n"/>
+      <c r="F843" s="44" t="n"/>
     </row>
     <row r="844">
       <c r="B844" s="31" t="inlineStr">
         <is>
-          <t>лак перфоманс ЭСФ 500 мл 11198/4138</t>
+          <t>Лак перфоманс экстрасильной фиксации 500мл 11198/4138</t>
         </is>
       </c>
       <c r="C844" s="32" t="n">
@@ -16672,7 +16684,7 @@
     <row r="845">
       <c r="B845" s="31" t="inlineStr">
         <is>
-          <t>Пена EIMI д/укладки №2 НФ 300 мл NATURAL VOLUME 11199/1642</t>
+          <t>Пена EIMI для укладки №2 нормальной фиксации 300мл NATURAL VOLUME 11199/1642</t>
         </is>
       </c>
       <c r="C845" s="32" t="n">
@@ -16691,7 +16703,7 @@
     <row r="846">
       <c r="B846" s="31" t="inlineStr">
         <is>
-          <t>Пена EIMI д/укладки №2 НФ 500мл NATURAL VOLUME 11020/9594</t>
+          <t>Пена EIMI для укладки №2 нормальной фиксации 500мл NATURAL VOLUME 11020/9594</t>
         </is>
       </c>
       <c r="C846" s="36" t="n">
@@ -16710,7 +16722,7 @@
     <row r="847" ht="22.5" customHeight="1">
       <c r="B847" s="31" t="inlineStr">
         <is>
-          <t>Спрей EIMI д/обьема текстуры, сахарный Sugar Lift 150мл 43750/6050</t>
+          <t>Спрей EIMI для объёма текстуры, сахарный Sugar Lift 150мл 43750/6050</t>
         </is>
       </c>
       <c r="C847" s="32" t="n">
@@ -16729,7 +16741,7 @@
     <row r="848">
       <c r="B848" s="31" t="inlineStr">
         <is>
-          <t>Спрей EIMI минеральный текстур. Ocean Spritz 150мл. 43747/1687</t>
+          <t>Спрей EIMI минеральный текстурирующий Ocean Spritz 150мл 43747/1687</t>
         </is>
       </c>
       <c r="C848" s="32" t="n">
@@ -16767,7 +16779,7 @@
     <row r="850">
       <c r="B850" s="31" t="inlineStr">
         <is>
-          <t>Спрей-мусс EIMI д.прик.объема Root Shoot  200мл 43130/9213</t>
+          <t>Спрей-мусс EIMI для прикорневого объёма Root Shoot 200мл 43130/9213</t>
         </is>
       </c>
       <c r="C850" s="32" t="n">
@@ -16789,10 +16801,10 @@
           <t>Illumina - Красители</t>
         </is>
       </c>
-      <c r="C851" s="17" t="n"/>
+      <c r="C851" s="45" t="n"/>
       <c r="D851" s="24" t="n"/>
-      <c r="E851" s="25" t="n"/>
-      <c r="F851" s="37" t="n"/>
+      <c r="E851" s="24" t="n"/>
+      <c r="F851" s="44" t="n"/>
     </row>
     <row r="852">
       <c r="B852" s="7" t="inlineStr">
@@ -17006,7 +17018,7 @@
     <row r="863">
       <c r="B863" s="7" t="inlineStr">
         <is>
-          <t>Illumina 5/7 Светло-коричневый коричневый 60мл 5/7</t>
+          <t>Illumina 5/7 Светло-коричневый 60мл 5/7</t>
         </is>
       </c>
       <c r="C863" s="8" t="n">
@@ -17484,15 +17496,15 @@
           <t>INVIGO - Уход</t>
         </is>
       </c>
-      <c r="C888" s="17" t="n"/>
+      <c r="C888" s="45" t="n"/>
       <c r="D888" s="24" t="n"/>
-      <c r="E888" s="25" t="n"/>
-      <c r="F888" s="37" t="n"/>
+      <c r="E888" s="24" t="n"/>
+      <c r="F888" s="44" t="n"/>
     </row>
     <row r="889">
       <c r="B889" s="7" t="inlineStr">
         <is>
-          <t>Brilliance Шампунь д/защиты цвета окр.жестк.волос 1000мл 339290</t>
+          <t>Brilliance Шампунь для защиты цвета окрашенных жестких волос 1000мл 339290</t>
         </is>
       </c>
       <c r="C889" s="10" t="n">
@@ -17511,7 +17523,7 @@
     <row r="890">
       <c r="B890" s="7" t="inlineStr">
         <is>
-          <t>Brilliance Шампунь д/защиты цвета окр.жестк.волос 300мл 339238</t>
+          <t>Brilliance Шампунь для защиты цвета окрашенных жестких волос 300мл 339238</t>
         </is>
       </c>
       <c r="C890" s="8" t="n">
@@ -17530,7 +17542,7 @@
     <row r="891" ht="22.5" customHeight="1">
       <c r="B891" s="7" t="inlineStr">
         <is>
-          <t>Brilliance Шампунь д/защиты цвета окр.норм. и тонких волос 1000мл 339283</t>
+          <t>Brilliance Шампунь для защиты цвета окрашенных нормальных и тонких волос 1000мл 339283</t>
         </is>
       </c>
       <c r="C891" s="10" t="n">
@@ -17549,7 +17561,7 @@
     <row r="892" ht="22.5" customHeight="1">
       <c r="B892" s="7" t="inlineStr">
         <is>
-          <t>Brilliance Шампунь д/защиты цвета окр.норм. и тонких волос 300мл 339221</t>
+          <t>Brilliance Шампунь для защиты цвета окрашенных нормальных и тонких волос 300мл 339221</t>
         </is>
       </c>
       <c r="C892" s="8" t="n">
@@ -17606,7 +17618,7 @@
     <row r="895">
       <c r="B895" s="31" t="inlineStr">
         <is>
-          <t>Дозатор д/WELLAPLEX 500 мл. 012341</t>
+          <t>Дозатор для WELLAPLEX 500мл 012341</t>
         </is>
       </c>
       <c r="C895" s="32" t="n">
@@ -17625,7 +17637,7 @@
     <row r="896">
       <c r="B896" s="31" t="inlineStr">
         <is>
-          <t>Дозатор д/кондиционера SYSTEM 271484 85282</t>
+          <t>Дозатор для кондиционера SYSTEM 271484 85282</t>
         </is>
       </c>
       <c r="C896" s="32" t="n">
@@ -17644,7 +17656,7 @@
     <row r="897">
       <c r="B897" s="31" t="inlineStr">
         <is>
-          <t>Дозатор д/маски 500 мл. 104509</t>
+          <t>Дозатор для маски 500мл 104509</t>
         </is>
       </c>
       <c r="C897" s="32" t="n">
@@ -17663,7 +17675,7 @@
     <row r="898">
       <c r="B898" s="31" t="inlineStr">
         <is>
-          <t>Дозатор д/шампуней 1000 мл. 99350093395</t>
+          <t>Дозатор для шампуня 1000мл 99350093395</t>
         </is>
       </c>
       <c r="C898" s="32" t="n">
@@ -17682,7 +17694,7 @@
     <row r="899">
       <c r="B899" s="31" t="inlineStr">
         <is>
-          <t>Дозатор д/шампуней 500 мл. 034916</t>
+          <t>Дозатор для шампуня 500мл 034916</t>
         </is>
       </c>
       <c r="C899" s="32" t="n">
@@ -17704,15 +17716,15 @@
           <t>KP Me+/CT - Красители и специальные продукты</t>
         </is>
       </c>
-      <c r="C900" s="17" t="n"/>
+      <c r="C900" s="45" t="n"/>
       <c r="D900" s="24" t="n"/>
-      <c r="E900" s="25" t="n"/>
-      <c r="F900" s="37" t="n"/>
+      <c r="E900" s="24" t="n"/>
+      <c r="F900" s="44" t="n"/>
     </row>
     <row r="901">
       <c r="B901" s="31" t="inlineStr">
         <is>
-          <t>Блондирующий крем масленный 7+ 200 мл 6289/x9225</t>
+          <t>Блондирующий крем масленный 7+ 200мл 6289/x9225</t>
         </is>
       </c>
       <c r="C901" s="36" t="n">
@@ -18624,7 +18636,7 @@
     <row r="949">
       <c r="B949" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 0/11 Пепельный интенс. 60 мл 0-11</t>
+          <t>Краска колестон 0/11 Пепельный интенсивный 60мл 0-11</t>
         </is>
       </c>
       <c r="C949" s="8" t="n">
@@ -19194,7 +19206,7 @@
     <row r="979" ht="22.5" customHeight="1">
       <c r="B979" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 3/00 Темно-коричневый интенс. натуральный 60мл 3-00</t>
+          <t>Краска колестон 3/00 Темно-коричневый интенсивный натуральный 60мл 3-00</t>
         </is>
       </c>
       <c r="C979" s="8" t="n">
@@ -19422,7 +19434,7 @@
     <row r="991">
       <c r="B991" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 5/3 корич. золотистый 60мл 5-3</t>
+          <t>Краска колестон 5/3 коричневый золотистый 60мл 5-3</t>
         </is>
       </c>
       <c r="C991" s="8" t="n">
@@ -19536,7 +19548,7 @@
     <row r="997">
       <c r="B997" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 6/00 Темный блонд натуральный интенс. 60мл 6-00</t>
+          <t>Краска колестон 6/00 Темный блонд натуральный интенсивный 60мл 6-00</t>
         </is>
       </c>
       <c r="C997" s="8" t="n">
@@ -19574,7 +19586,7 @@
     <row r="999">
       <c r="B999" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 6/34 Медовый пунш 60 мл. 6-34</t>
+          <t>Краска колестон 6/34 Медовый пунш 60мл 6-34</t>
         </is>
       </c>
       <c r="C999" s="8" t="n">
@@ -19707,7 +19719,7 @@
     <row r="1006">
       <c r="B1006" s="31" t="inlineStr">
         <is>
-          <t>Краска колестон 7/00 Блонд натуральный интенс. 60мл 7-00</t>
+          <t>Краска колестон 7/00 Блонд натуральный интенсивный 60мл 7-00</t>
         </is>
       </c>
       <c r="C1006" s="32" t="n">
@@ -20315,7 +20327,7 @@
     <row r="1038" ht="22.5" customHeight="1">
       <c r="B1038" s="7" t="inlineStr">
         <is>
-          <t>Краска колестон 9/00 Очень светлый блонд натуральный интенс. 60мл 9-00</t>
+          <t>Краска колестон 9/00 Очень светлый блонд натуральный интенсивный 60мл 9-00</t>
         </is>
       </c>
       <c r="C1038" s="8" t="n">
@@ -20638,7 +20650,7 @@
     <row r="1055">
       <c r="B1055" s="31" t="inlineStr">
         <is>
-          <t>Окислитель Welloxon Perfect 9% 1000 мл. 6498/6484</t>
+          <t>Окислитель Welloxon Perfect 9% 1000мл 6498/6484</t>
         </is>
       </c>
       <c r="C1055" s="32" t="n">
@@ -20657,7 +20669,7 @@
     <row r="1056">
       <c r="B1056" s="7" t="inlineStr">
         <is>
-          <t>Оксид Color Touch 1,9 % 1000 мл. 6021/6298</t>
+          <t>Оксид Color Touch 1,9 % 1000мл 6021/6298</t>
         </is>
       </c>
       <c r="C1056" s="8" t="n">
@@ -20676,7 +20688,7 @@
     <row r="1057">
       <c r="B1057" s="31" t="inlineStr">
         <is>
-          <t>Оксид Color Touch 4 % 1000 мл. 6019/6291</t>
+          <t>Оксид Color Touch 4 % 1000мл 6019/6291</t>
         </is>
       </c>
       <c r="C1057" s="32" t="n">
@@ -20717,10 +20729,10 @@
           <t>SHINEFINITY - Гель-крем краска, цветное глазирование</t>
         </is>
       </c>
-      <c r="C1059" s="17" t="n"/>
+      <c r="C1059" s="45" t="n"/>
       <c r="D1059" s="24" t="n"/>
-      <c r="E1059" s="25" t="n"/>
-      <c r="F1059" s="37" t="n"/>
+      <c r="E1059" s="24" t="n"/>
+      <c r="F1059" s="44" t="n"/>
     </row>
     <row r="1060">
       <c r="B1060" s="7" t="inlineStr">
@@ -21032,10 +21044,10 @@
           <t>Корея</t>
         </is>
       </c>
-      <c r="C1076" s="16" t="n"/>
+      <c r="C1076" s="43" t="n"/>
       <c r="D1076" s="24" t="n"/>
-      <c r="E1076" s="25" t="n"/>
-      <c r="F1076" s="26" t="n"/>
+      <c r="E1076" s="24" t="n"/>
+      <c r="F1076" s="44" t="n"/>
     </row>
     <row r="1077" ht="14.25" customHeight="1">
       <c r="B1077" s="12" t="inlineStr">
@@ -21043,15 +21055,15 @@
           <t>La`Dor</t>
         </is>
       </c>
-      <c r="C1077" s="17" t="n"/>
+      <c r="C1077" s="45" t="n"/>
       <c r="D1077" s="24" t="n"/>
-      <c r="E1077" s="25" t="n"/>
-      <c r="F1077" s="37" t="n"/>
+      <c r="E1077" s="24" t="n"/>
+      <c r="F1077" s="44" t="n"/>
     </row>
     <row r="1078" ht="22.5" customHeight="1">
       <c r="B1078" s="7" t="inlineStr">
         <is>
-          <t>Филлер для восстановления волос Perfect Hair Fill-Up 13 мл 845623/лд2</t>
+          <t>Филлер для восстановления волос Perfect Hair Fill-Up 13мл 845623/лд2</t>
         </is>
       </c>
       <c r="C1078" s="8" t="n">
@@ -21073,15 +21085,15 @@
           <t>ОДНОРАЗОВАЯ ПРОДУКЦИЯ</t>
         </is>
       </c>
-      <c r="C1079" s="16" t="n"/>
+      <c r="C1079" s="43" t="n"/>
       <c r="D1079" s="24" t="n"/>
-      <c r="E1079" s="25" t="n"/>
-      <c r="F1079" s="26" t="n"/>
+      <c r="E1079" s="24" t="n"/>
+      <c r="F1079" s="44" t="n"/>
     </row>
     <row r="1080">
       <c r="B1080" s="7" t="inlineStr">
         <is>
-          <t>Бахилы ПЭ 100шт. 01-606</t>
+          <t>Бахилы ПЭ 100шт 01-606</t>
         </is>
       </c>
       <c r="C1080" s="8" t="n">
@@ -21157,7 +21169,7 @@
     <row r="1084">
       <c r="B1084" s="7" t="inlineStr">
         <is>
-          <t>Пелерина п/э 25шт 01-681/10-654</t>
+          <t>Пелерина полиэтиленовая 25шт 01-681/10-654</t>
         </is>
       </c>
       <c r="C1084" s="8" t="n">
@@ -21252,7 +21264,7 @@
     <row r="1089">
       <c r="B1089" s="7" t="inlineStr">
         <is>
-          <t>перчатки виниловые,смотр.н/о "L" 100шт 01-943</t>
+          <t>перчатки виниловые, смотр.н/о "L" 100шт 01-943</t>
         </is>
       </c>
       <c r="C1089" s="8" t="n">
@@ -21290,7 +21302,7 @@
     <row r="1091">
       <c r="B1091" s="7" t="inlineStr">
         <is>
-          <t>перчатки нитриловые голубые "M" 200 шт. (100 пар) 0200-234</t>
+          <t>перчатки нитриловые голубые "M" 200шт (100 пар) 0200-234</t>
         </is>
       </c>
       <c r="C1091" s="8" t="n">
@@ -21328,7 +21340,7 @@
     <row r="1093">
       <c r="B1093" s="7" t="inlineStr">
         <is>
-          <t>перчатки нитриловые фиолетовые "S" 100 пар (200 шт.) 0200-235</t>
+          <t>перчатки нитриловые фиолетовые "S" 100 пар (200шт) 0200-235</t>
         </is>
       </c>
       <c r="C1093" s="10" t="n">
@@ -21385,7 +21397,7 @@
     <row r="1096">
       <c r="B1096" s="7" t="inlineStr">
         <is>
-          <t>перчатки нитриловые черные "S" 100 шт. 604-188</t>
+          <t>перчатки нитриловые черные "S" 100шт 604-188</t>
         </is>
       </c>
       <c r="C1096" s="8" t="n">
@@ -21423,7 +21435,7 @@
     <row r="1098">
       <c r="B1098" s="7" t="inlineStr">
         <is>
-          <t>Полотенце COTTO 35x70 см. №50 шт. 601-066</t>
+          <t>Полотенце COTTO 35x70 см №50шт 601-066</t>
         </is>
       </c>
       <c r="C1098" s="8" t="n">
@@ -21442,7 +21454,7 @@
     <row r="1099">
       <c r="B1099" s="7" t="inlineStr">
         <is>
-          <t>Полотенце Стандарт 35x70 см. №100 шт. 01-359/SL-S35-100</t>
+          <t>Полотенце Стандарт 35x70 см №100шт 01-359/SL-S35-100</t>
         </is>
       </c>
       <c r="C1099" s="8" t="n">
@@ -21461,7 +21473,7 @@
     <row r="1100">
       <c r="B1100" s="7" t="inlineStr">
         <is>
-          <t>Полотенце Стандарт 45x90 см. №50 шт. 01-349/EL-S45-50</t>
+          <t>Полотенце Стандарт 45x90 см №50шт 01-349/EL-S45-50</t>
         </is>
       </c>
       <c r="C1100" s="8" t="n">
@@ -21537,7 +21549,7 @@
     <row r="1104">
       <c r="B1104" s="31" t="inlineStr">
         <is>
-          <t>Салфетки 20х20 200 шт. в рулоне 00-144-200</t>
+          <t>Салфетки 20х20 200шт в рулоне 00-144-200</t>
         </is>
       </c>
       <c r="C1104" s="32" t="n">
@@ -21556,7 +21568,7 @@
     <row r="1105">
       <c r="B1105" s="7" t="inlineStr">
         <is>
-          <t>Салфетки 30х40 100шт. 00-147</t>
+          <t>Салфетки 30х40 100шт 00-147</t>
         </is>
       </c>
       <c r="C1105" s="8" t="n">
@@ -21575,7 +21587,7 @@
     <row r="1106">
       <c r="B1106" s="7" t="inlineStr">
         <is>
-          <t>Фартук п/э 70х120 50шт. 01-626</t>
+          <t>Фартук полиэтиленовая 70х120 50шт 01-626</t>
         </is>
       </c>
       <c r="C1106" s="8" t="n">
@@ -21708,7 +21720,7 @@
     <row r="1113">
       <c r="B1113" s="7" t="inlineStr">
         <is>
-          <t>Шапочки "Шарлотка" 50 шт ,ЧЕРНЫЕ 603-208</t>
+          <t>Шапочки "Шарлотка" 50шт, ЧЕРНЫЕ 603-208</t>
         </is>
       </c>
       <c r="C1113" s="8" t="n">
@@ -21727,7 +21739,7 @@
     <row r="1114">
       <c r="B1114" s="38" t="inlineStr">
         <is>
-          <t>Шапочки "Шарлотка" 50 шт БЕЛЫЕ 601-729</t>
+          <t>Шапочки "Шарлотка" 50шт БЕЛЫЕ 601-729</t>
         </is>
       </c>
       <c r="C1114" s="39" t="n">
@@ -21743,25 +21755,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="1115"/>
-    <row r="1116"/>
-    <row r="1117"/>
-    <row r="1118"/>
-    <row r="1119"/>
     <row r="1120" ht="22.5" customHeight="1"/>
     <row r="1121" ht="22.5" customHeight="1"/>
     <row r="1122" ht="22.5" customHeight="1"/>
-    <row r="1123"/>
-    <row r="1124"/>
-    <row r="1125"/>
-    <row r="1126"/>
-    <row r="1127"/>
-    <row r="1128"/>
-    <row r="1129"/>
-    <row r="1130"/>
-    <row r="1131"/>
-    <row r="1132"/>
-    <row r="1133"/>
     <row r="1135" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">

--- a/public/prices/price-current.xlsx
+++ b/public/prices/price-current.xlsx
@@ -87,7 +87,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -349,22 +349,13 @@
       </top>
       <bottom style="medium"/>
     </border>
-    <border>
-      <left/>
-      <right style="medium"/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -462,9 +453,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -842,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F1114"/>
+  <dimension ref="A1:F1114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="11.25"/>
   <cols>
     <col width="2.6640625" customWidth="1" min="1" max="1"/>
@@ -908,10 +896,10 @@
           <t>CAREPROST</t>
         </is>
       </c>
-      <c r="C6" s="43" t="n"/>
+      <c r="C6" s="16" t="n"/>
       <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="44" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="7" t="inlineStr">
@@ -938,10 +926,10 @@
           <t>CONCEPT</t>
         </is>
       </c>
-      <c r="C8" s="43" t="n"/>
+      <c r="C8" s="16" t="n"/>
       <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="44" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="26" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="7" t="inlineStr">
@@ -1346,10 +1334,10 @@
           <t>DIKSON</t>
         </is>
       </c>
-      <c r="C30" s="43" t="n"/>
+      <c r="C30" s="16" t="n"/>
       <c r="D30" s="24" t="n"/>
-      <c r="E30" s="24" t="n"/>
-      <c r="F30" s="44" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="26" t="n"/>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="B31" s="7" t="inlineStr">
@@ -1395,10 +1383,10 @@
           <t>ISKARTES PROFESSIONAL</t>
         </is>
       </c>
-      <c r="C33" s="43" t="n"/>
+      <c r="C33" s="16" t="n"/>
       <c r="D33" s="24" t="n"/>
-      <c r="E33" s="24" t="n"/>
-      <c r="F33" s="44" t="n"/>
+      <c r="E33" s="25" t="n"/>
+      <c r="F33" s="26" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="31" t="inlineStr">
@@ -1501,10 +1489,10 @@
           <t>KAPOUS</t>
         </is>
       </c>
-      <c r="C39" s="43" t="n"/>
+      <c r="C39" s="16" t="n"/>
       <c r="D39" s="24" t="n"/>
-      <c r="E39" s="24" t="n"/>
-      <c r="F39" s="44" t="n"/>
+      <c r="E39" s="25" t="n"/>
+      <c r="F39" s="26" t="n"/>
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="B40" s="7" t="inlineStr">
@@ -2169,10 +2157,10 @@
           <t>L'OREAL</t>
         </is>
       </c>
-      <c r="C75" s="43" t="n"/>
+      <c r="C75" s="16" t="n"/>
       <c r="D75" s="24" t="n"/>
-      <c r="E75" s="24" t="n"/>
-      <c r="F75" s="44" t="n"/>
+      <c r="E75" s="25" t="n"/>
+      <c r="F75" s="26" t="n"/>
     </row>
     <row r="76">
       <c r="B76" s="7" t="inlineStr">
@@ -2332,10 +2320,10 @@
           <t>LEBEL</t>
         </is>
       </c>
-      <c r="C84" s="43" t="n"/>
+      <c r="C84" s="16" t="n"/>
       <c r="D84" s="24" t="n"/>
-      <c r="E84" s="24" t="n"/>
-      <c r="F84" s="44" t="n"/>
+      <c r="E84" s="25" t="n"/>
+      <c r="F84" s="26" t="n"/>
     </row>
     <row r="85">
       <c r="B85" s="7" t="inlineStr">
@@ -4129,10 +4117,10 @@
           <t>LEVISSIME</t>
         </is>
       </c>
-      <c r="C179" s="43" t="n"/>
+      <c r="C179" s="16" t="n"/>
       <c r="D179" s="24" t="n"/>
-      <c r="E179" s="24" t="n"/>
-      <c r="F179" s="44" t="n"/>
+      <c r="E179" s="25" t="n"/>
+      <c r="F179" s="26" t="n"/>
     </row>
     <row r="180">
       <c r="B180" s="7" t="inlineStr">
@@ -4178,10 +4166,10 @@
           <t>LONDA</t>
         </is>
       </c>
-      <c r="C182" s="43" t="n"/>
+      <c r="C182" s="16" t="n"/>
       <c r="D182" s="24" t="n"/>
-      <c r="E182" s="24" t="n"/>
-      <c r="F182" s="44" t="n"/>
+      <c r="E182" s="25" t="n"/>
+      <c r="F182" s="26" t="n"/>
     </row>
     <row r="183">
       <c r="B183" s="31" t="inlineStr">
@@ -7704,10 +7692,10 @@
           <t>MATRIX</t>
         </is>
       </c>
-      <c r="C368" s="43" t="n"/>
+      <c r="C368" s="16" t="n"/>
       <c r="D368" s="24" t="n"/>
-      <c r="E368" s="24" t="n"/>
-      <c r="F368" s="44" t="n"/>
+      <c r="E368" s="25" t="n"/>
+      <c r="F368" s="26" t="n"/>
     </row>
     <row r="369" ht="14.25" customHeight="1">
       <c r="B369" s="12" t="inlineStr">
@@ -7715,10 +7703,10 @@
           <t>Total Results New</t>
         </is>
       </c>
-      <c r="C369" s="45" t="n"/>
+      <c r="C369" s="17" t="n"/>
       <c r="D369" s="24" t="n"/>
-      <c r="E369" s="24" t="n"/>
-      <c r="F369" s="44" t="n"/>
+      <c r="E369" s="25" t="n"/>
+      <c r="F369" s="37" t="n"/>
     </row>
     <row r="370">
       <c r="B370" s="31" t="inlineStr">
@@ -7973,10 +7961,10 @@
           <t>MATRIX</t>
         </is>
       </c>
-      <c r="C383" s="45" t="n"/>
+      <c r="C383" s="17" t="n"/>
       <c r="D383" s="24" t="n"/>
-      <c r="E383" s="24" t="n"/>
-      <c r="F383" s="44" t="n"/>
+      <c r="E383" s="25" t="n"/>
+      <c r="F383" s="37" t="n"/>
     </row>
     <row r="384">
       <c r="B384" s="7" t="inlineStr">
@@ -10853,10 +10841,10 @@
           <t>OLLIN</t>
         </is>
       </c>
-      <c r="C535" s="43" t="n"/>
+      <c r="C535" s="16" t="n"/>
       <c r="D535" s="24" t="n"/>
-      <c r="E535" s="24" t="n"/>
-      <c r="F535" s="44" t="n"/>
+      <c r="E535" s="25" t="n"/>
+      <c r="F535" s="26" t="n"/>
     </row>
     <row r="536">
       <c r="B536" s="7" t="inlineStr">
@@ -14759,10 +14747,10 @@
           <t>SCHWARZKOPF</t>
         </is>
       </c>
-      <c r="C741" s="43" t="n"/>
+      <c r="C741" s="16" t="n"/>
       <c r="D741" s="24" t="n"/>
-      <c r="E741" s="24" t="n"/>
-      <c r="F741" s="44" t="n"/>
+      <c r="E741" s="25" t="n"/>
+      <c r="F741" s="26" t="n"/>
     </row>
     <row r="742" ht="28.5" customHeight="1">
       <c r="B742" s="12" t="inlineStr">
@@ -14770,10 +14758,10 @@
           <t>IGORA/BLONDME - Красители и специальные продукты</t>
         </is>
       </c>
-      <c r="C742" s="45" t="n"/>
+      <c r="C742" s="17" t="n"/>
       <c r="D742" s="24" t="n"/>
-      <c r="E742" s="24" t="n"/>
-      <c r="F742" s="44" t="n"/>
+      <c r="E742" s="25" t="n"/>
+      <c r="F742" s="37" t="n"/>
     </row>
     <row r="743">
       <c r="B743" s="31" t="inlineStr">
@@ -16510,10 +16498,10 @@
           <t>OSIS - Укладка</t>
         </is>
       </c>
-      <c r="C834" s="45" t="n"/>
+      <c r="C834" s="17" t="n"/>
       <c r="D834" s="24" t="n"/>
-      <c r="E834" s="24" t="n"/>
-      <c r="F834" s="44" t="n"/>
+      <c r="E834" s="25" t="n"/>
+      <c r="F834" s="37" t="n"/>
     </row>
     <row r="835">
       <c r="B835" s="31" t="inlineStr">
@@ -16578,10 +16566,10 @@
           <t>SILHOUETTE/Professionnelle - Укладка</t>
         </is>
       </c>
-      <c r="C838" s="45" t="n"/>
+      <c r="C838" s="17" t="n"/>
       <c r="D838" s="24" t="n"/>
-      <c r="E838" s="24" t="n"/>
-      <c r="F838" s="44" t="n"/>
+      <c r="E838" s="25" t="n"/>
+      <c r="F838" s="37" t="n"/>
     </row>
     <row r="839">
       <c r="B839" s="7" t="inlineStr">
@@ -16646,10 +16634,10 @@
           <t>WELLA</t>
         </is>
       </c>
-      <c r="C842" s="43" t="n"/>
+      <c r="C842" s="16" t="n"/>
       <c r="D842" s="24" t="n"/>
-      <c r="E842" s="24" t="n"/>
-      <c r="F842" s="44" t="n"/>
+      <c r="E842" s="25" t="n"/>
+      <c r="F842" s="26" t="n"/>
     </row>
     <row r="843" ht="14.25" customHeight="1">
       <c r="B843" s="12" t="inlineStr">
@@ -16657,10 +16645,10 @@
           <t>EIMI - Укладка</t>
         </is>
       </c>
-      <c r="C843" s="45" t="n"/>
+      <c r="C843" s="17" t="n"/>
       <c r="D843" s="24" t="n"/>
-      <c r="E843" s="24" t="n"/>
-      <c r="F843" s="44" t="n"/>
+      <c r="E843" s="25" t="n"/>
+      <c r="F843" s="37" t="n"/>
     </row>
     <row r="844">
       <c r="B844" s="31" t="inlineStr">
@@ -16801,10 +16789,10 @@
           <t>Illumina - Красители</t>
         </is>
       </c>
-      <c r="C851" s="45" t="n"/>
+      <c r="C851" s="17" t="n"/>
       <c r="D851" s="24" t="n"/>
-      <c r="E851" s="24" t="n"/>
-      <c r="F851" s="44" t="n"/>
+      <c r="E851" s="25" t="n"/>
+      <c r="F851" s="37" t="n"/>
     </row>
     <row r="852">
       <c r="B852" s="7" t="inlineStr">
@@ -17496,10 +17484,10 @@
           <t>INVIGO - Уход</t>
         </is>
       </c>
-      <c r="C888" s="45" t="n"/>
+      <c r="C888" s="17" t="n"/>
       <c r="D888" s="24" t="n"/>
-      <c r="E888" s="24" t="n"/>
-      <c r="F888" s="44" t="n"/>
+      <c r="E888" s="25" t="n"/>
+      <c r="F888" s="37" t="n"/>
     </row>
     <row r="889">
       <c r="B889" s="7" t="inlineStr">
@@ -17716,10 +17704,10 @@
           <t>KP Me+/CT - Красители и специальные продукты</t>
         </is>
       </c>
-      <c r="C900" s="45" t="n"/>
+      <c r="C900" s="17" t="n"/>
       <c r="D900" s="24" t="n"/>
-      <c r="E900" s="24" t="n"/>
-      <c r="F900" s="44" t="n"/>
+      <c r="E900" s="25" t="n"/>
+      <c r="F900" s="37" t="n"/>
     </row>
     <row r="901">
       <c r="B901" s="31" t="inlineStr">
@@ -20729,10 +20717,10 @@
           <t>SHINEFINITY - Гель-крем краска, цветное глазирование</t>
         </is>
       </c>
-      <c r="C1059" s="45" t="n"/>
+      <c r="C1059" s="17" t="n"/>
       <c r="D1059" s="24" t="n"/>
-      <c r="E1059" s="24" t="n"/>
-      <c r="F1059" s="44" t="n"/>
+      <c r="E1059" s="25" t="n"/>
+      <c r="F1059" s="37" t="n"/>
     </row>
     <row r="1060">
       <c r="B1060" s="7" t="inlineStr">
@@ -21044,10 +21032,10 @@
           <t>Корея</t>
         </is>
       </c>
-      <c r="C1076" s="43" t="n"/>
+      <c r="C1076" s="16" t="n"/>
       <c r="D1076" s="24" t="n"/>
-      <c r="E1076" s="24" t="n"/>
-      <c r="F1076" s="44" t="n"/>
+      <c r="E1076" s="25" t="n"/>
+      <c r="F1076" s="26" t="n"/>
     </row>
     <row r="1077" ht="14.25" customHeight="1">
       <c r="B1077" s="12" t="inlineStr">
@@ -21055,10 +21043,10 @@
           <t>La`Dor</t>
         </is>
       </c>
-      <c r="C1077" s="45" t="n"/>
+      <c r="C1077" s="17" t="n"/>
       <c r="D1077" s="24" t="n"/>
-      <c r="E1077" s="24" t="n"/>
-      <c r="F1077" s="44" t="n"/>
+      <c r="E1077" s="25" t="n"/>
+      <c r="F1077" s="37" t="n"/>
     </row>
     <row r="1078" ht="22.5" customHeight="1">
       <c r="B1078" s="7" t="inlineStr">
@@ -21085,10 +21073,10 @@
           <t>ОДНОРАЗОВАЯ ПРОДУКЦИЯ</t>
         </is>
       </c>
-      <c r="C1079" s="43" t="n"/>
+      <c r="C1079" s="16" t="n"/>
       <c r="D1079" s="24" t="n"/>
-      <c r="E1079" s="24" t="n"/>
-      <c r="F1079" s="44" t="n"/>
+      <c r="E1079" s="25" t="n"/>
+      <c r="F1079" s="26" t="n"/>
     </row>
     <row r="1080">
       <c r="B1080" s="7" t="inlineStr">
@@ -21755,9 +21743,25 @@
         <v>17</v>
       </c>
     </row>
+    <row r="1115"/>
+    <row r="1116"/>
+    <row r="1117"/>
+    <row r="1118"/>
+    <row r="1119"/>
     <row r="1120" ht="22.5" customHeight="1"/>
     <row r="1121" ht="22.5" customHeight="1"/>
     <row r="1122" ht="22.5" customHeight="1"/>
+    <row r="1123"/>
+    <row r="1124"/>
+    <row r="1125"/>
+    <row r="1126"/>
+    <row r="1127"/>
+    <row r="1128"/>
+    <row r="1129"/>
+    <row r="1130"/>
+    <row r="1131"/>
+    <row r="1132"/>
+    <row r="1133"/>
     <row r="1135" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">

--- a/public/prices/price-current.xlsx
+++ b/public/prices/price-current.xlsx
@@ -3050,7 +3050,7 @@
     <row r="120">
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>Краска д/волос СТОЙКАЯ ABe-10 8200/0-ABe-10</t>
+          <t>Материя 80мл ABe-10 8200/0-ABe-10</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
@@ -3941,7 +3941,7 @@
     <row r="167">
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>Шампунь "Jojoba" жожоба, для сухих волос, 1000мл 1576</t>
+          <t>Шампунь "Jojoba" жожоба, для сухих волос 1000мл 1576</t>
         </is>
       </c>
       <c r="C167" s="10" t="n">
@@ -6829,7 +6829,7 @@
     <row r="321">
       <c r="B321" s="31" t="inlineStr">
         <is>
-          <t>Кондиционер д/окрашенных волос 1000мл 4765/10559</t>
+          <t>Кондиционер для окрашенных волос 1000мл 4765/10559</t>
         </is>
       </c>
       <c r="C321" s="36" t="n">
@@ -6841,9 +6841,7 @@
         </is>
       </c>
       <c r="E321" s="34" t="n"/>
-      <c r="F321" s="35" t="n">
-        <v>9</v>
-      </c>
+      <c r="F321" s="39" t="n"/>
     </row>
     <row r="322">
       <c r="B322" s="31" t="inlineStr">

--- a/public/prices/price-current.xlsx
+++ b/public/prices/price-current.xlsx
@@ -1514,7 +1514,7 @@
     <row r="34">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Лосьон д/удаления краски с кожи головы 200млголовы c/sl</t>
+          <t>Лосьон для удаления краски с кожи головы 200мл c/sl</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -1537,7 +1537,7 @@
     <row r="35">
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Эмульсия д/удаления краски с волос 3шт*100мл COLOR OFF c/f</t>
+          <t>Эмульсия для удаления краски с волос COLOR OFF 3шт*100мл c/f</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
